--- a/safehome_data.xlsx
+++ b/safehome_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A722"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,11 @@
           <t>BLI 1000</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -429,6 +434,11 @@
           <t>T 1</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -436,6 +446,11 @@
           <t>RZ 1/B</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -443,6 +458,11 @@
           <t>SLIDE KIT/FORCE F/CRV4</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -450,6 +470,11 @@
           <t>FORCE 3000 SÍN</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -457,6 +482,11 @@
           <t>SLIDE KIT/FORCE/CRV4</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -464,6 +494,11 @@
           <t>RZ 1/J</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -471,6 +506,11 @@
           <t>RZ 2</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -478,6 +518,11 @@
           <t>KIT TERRIER</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -485,6 +530,11 @@
           <t>BLINDO</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -492,6 +542,11 @@
           <t>BLUES 3</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -499,6 +554,11 @@
           <t>CB 24</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -506,6 +566,11 @@
           <t>EDGE OC/2</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -513,6 +578,11 @@
           <t>KIT SLI 324</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -520,6 +590,11 @@
           <t>PASSO R</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -527,6 +602,11 @@
           <t>RAP 4</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -534,6 +614,11 @@
           <t>RSQ 449 OC/2</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -541,6 +626,11 @@
           <t>SLI 324</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -548,6 +638,11 @@
           <t>STICKERS</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -555,6 +650,11 @@
           <t>T 10</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -562,6 +662,11 @@
           <t>T 124/SS</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -569,6 +674,11 @@
           <t>T 400</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -576,6 +686,11 @@
           <t>TRS 435/2</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -583,6 +698,11 @@
           <t>VEDO 180</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -590,6 +710,11 @@
           <t>CH 161M16</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -597,6 +722,11 @@
           <t>CH 166M</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -604,6 +734,11 @@
           <t>CH 300-60</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -611,6 +746,11 @@
           <t>CH 300-Y60</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -618,6 +758,11 @@
           <t>CH 300-Y80</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -625,6 +770,11 @@
           <t>RC 2</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -632,6 +782,11 @@
           <t>SLIDE KIT/EDGE</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -639,6 +794,11 @@
           <t>SOM TOT/400</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -646,6 +806,11 @@
           <t>STAR</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -653,6 +818,11 @@
           <t>BDJ VEZÉRLÉS</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -660,6 +830,11 @@
           <t>C48</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -667,6 +842,11 @@
           <t>C48 KIT</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -674,6 +854,11 @@
           <t>KANO 1/A</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -681,6 +866,11 @@
           <t>KANO 21/48</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -688,6 +878,11 @@
           <t>KANO 24P</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -695,6 +890,11 @@
           <t>COM 110 20</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -702,6 +902,11 @@
           <t>COM 402 140</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -709,6 +914,11 @@
           <t>S 300 SX</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -716,6 +926,11 @@
           <t>SR 600</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -723,6 +938,11 @@
           <t>FORCE 500 DC</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -730,6 +950,11 @@
           <t>FORCE WIFI</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -737,6 +962,11 @@
           <t>ICON</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -744,6 +974,11 @@
           <t>SNAP 3/4</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -751,6 +986,11 @@
           <t>OC RELÉ/2</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -758,6 +998,11 @@
           <t>FORCE RB3</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -765,6 +1010,11 @@
           <t>ICON W</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -772,6 +1022,11 @@
           <t>HERO</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -779,6 +1034,11 @@
           <t>SLIDE KIT/EDGE/CRV4</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -786,6 +1046,11 @@
           <t>BD LOCK</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -793,6 +1058,11 @@
           <t>SWING 300/FORCE F</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -800,6 +1070,11 @@
           <t>ULTIMATE 600/SPEED</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -807,6 +1082,11 @@
           <t>ULTIMATE 1000/SPEED</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -814,6 +1094,11 @@
           <t>ICON X</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -821,6 +1106,11 @@
           <t>T 21 B</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -828,6 +1118,11 @@
           <t>FORCE 800 DC</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -835,6 +1130,11 @@
           <t>SWING 400/FORCE F</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -842,6 +1142,11 @@
           <t>FORCE FL</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -849,6 +1154,11 @@
           <t>ULTIMATE 600/SPEED PRO</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -856,6 +1166,11 @@
           <t>DOMOPARK V</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -863,6 +1178,11 @@
           <t>KIT ULTIMATE 600/SP</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -870,6 +1190,11 @@
           <t>LAMP TER</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -877,6 +1202,11 @@
           <t>SWING 600/FORCE F</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -884,6 +1214,11 @@
           <t>SL 524</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -891,6 +1226,11 @@
           <t>FORCE 4</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -898,6 +1238,11 @@
           <t>ACE 601</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -905,6 +1250,11 @@
           <t>BLUES 5</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -912,6 +1262,11 @@
           <t>DOMOPARK</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -919,6 +1274,11 @@
           <t>EDGE 2</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -926,6 +1286,11 @@
           <t>EDGE RB2</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -933,6 +1298,11 @@
           <t>EL SRE</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -940,6 +1310,11 @@
           <t>EVO 600</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -947,6 +1322,11 @@
           <t>FT 201 SINCRO</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -954,6 +1334,11 @@
           <t>KIT BLI 1000</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -961,6 +1346,11 @@
           <t>LPX LAMP</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -968,6 +1358,11 @@
           <t>PASSO</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -975,6 +1370,11 @@
           <t>PRG 230/M2</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -982,6 +1382,11 @@
           <t>RAPPER 4T</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -989,6 +1394,11 @@
           <t>RSQ 504 OC/2</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -996,6 +1406,11 @@
           <t>T 101/SS</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1003,6 +1418,11 @@
           <t>TRS 435/4</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1010,6 +1430,11 @@
           <t>CH 161M18</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1017,6 +1442,11 @@
           <t>CRV4</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1024,6 +1454,11 @@
           <t>IC 6200/1</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1031,6 +1466,11 @@
           <t>RC2 MAX</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1038,6 +1478,11 @@
           <t>STAR BOX</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1045,6 +1490,11 @@
           <t>WF/BT CONTROLL</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1052,6 +1502,11 @@
           <t>C60</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1059,6 +1514,11 @@
           <t>C60 KIT</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1066,6 +1526,11 @@
           <t>KANO 21/60</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1073,6 +1538,11 @@
           <t>KANO 24M</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1080,6 +1550,11 @@
           <t>KANO 48</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1087,6 +1562,11 @@
           <t>COM 115 20</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1094,6 +1574,11 @@
           <t>COM 420 140</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1101,6 +1586,11 @@
           <t>S 300 DX</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1108,6 +1598,11 @@
           <t>FORCE FS 1500</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1115,6 +1610,11 @@
           <t>KIT ULTIMATE 1000/SP</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1122,6 +1622,11 @@
           <t>TX TER</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1129,6 +1634,11 @@
           <t>VEDO 180 PRO</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1136,6 +1646,11 @@
           <t>SLIDE KIT/449/CRV4</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1143,6 +1658,11 @@
           <t>SWING 300/FORCE</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1150,6 +1670,11 @@
           <t>DOMOPARK S</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1157,6 +1682,11 @@
           <t>SLIDE KIT/504/CRV4</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1164,6 +1694,11 @@
           <t>CDR 861</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1171,6 +1706,11 @@
           <t>S 400 SX</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1178,6 +1718,11 @@
           <t>SWING 400/FORCE</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1185,6 +1730,11 @@
           <t>CDR 999</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1192,6 +1742,11 @@
           <t>S 400 DX</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1199,6 +1754,11 @@
           <t>RSQ 508 OC/2</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1206,6 +1766,11 @@
           <t>SWING 600/FORCE</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1213,6 +1778,11 @@
           <t>CDR 851</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1220,6 +1790,11 @@
           <t>CDR REFLEX</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1227,6 +1802,11 @@
           <t>S 600 SX</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1234,6 +1814,11 @@
           <t>S 600 DX</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1241,6 +1826,11 @@
           <t>S 300F SX</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1248,6 +1838,11 @@
           <t>ACE 801</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1255,6 +1850,11 @@
           <t>CC824EINTCB</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1262,6 +1862,11 @@
           <t>EDGE 4</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1269,6 +1874,11 @@
           <t>EDGE R4</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1276,6 +1886,11 @@
           <t>EL REF3</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1283,6 +1898,11 @@
           <t>EVO 800</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1290,6 +1910,11 @@
           <t>KIT EVO 600</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1297,6 +1922,11 @@
           <t>LPX LAMP/OR</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1304,6 +1934,11 @@
           <t>RSQ 504/2</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1311,6 +1946,11 @@
           <t>SNAPPER 3</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1318,6 +1958,11 @@
           <t>SSB T9K4</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1325,6 +1970,11 @@
           <t>STEALTH</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1332,6 +1982,11 @@
           <t>T 600</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1339,6 +1994,11 @@
           <t>TXQ 449/1</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1346,6 +2006,11 @@
           <t>CH 161M20</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1353,6 +2018,11 @@
           <t>CH 300-Y100</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1360,6 +2030,11 @@
           <t>CRV6</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1367,6 +2042,11 @@
           <t>KIT MULTI DRIVE PRO 1000</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1374,6 +2054,11 @@
           <t>MULTI COLOR</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1381,6 +2066,11 @@
           <t>STAR OC/2</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1388,6 +2078,11 @@
           <t>WF/BT PRO</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1395,6 +2090,11 @@
           <t>C60/F5 KIT</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1402,6 +2102,11 @@
           <t>C65</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1409,6 +2114,11 @@
           <t>KANO 2/A</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1416,6 +2126,11 @@
           <t>KANO 21/65</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1423,6 +2138,11 @@
           <t>COM 165 80</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1430,6 +2150,11 @@
           <t>COM 194 30</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1437,6 +2162,11 @@
           <t>COM 220</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1444,6 +2174,11 @@
           <t>COM 490 140</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1451,6 +2186,11 @@
           <t>COM 4C P</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1458,6 +2198,11 @@
           <t>S 300F DX</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1465,6 +2210,11 @@
           <t>SC 100</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1472,6 +2222,11 @@
           <t>CDRX 12</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1479,6 +2234,11 @@
           <t>KIT STEALTH/504</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1486,6 +2246,11 @@
           <t>STEALTH/VEZ</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1493,6 +2258,11 @@
           <t>COM 105 20</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1500,6 +2270,11 @@
           <t>S 400F SX</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1507,6 +2282,11 @@
           <t>NO TOUCH</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1514,6 +2294,11 @@
           <t>S 400F DX</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -1521,6 +2306,11 @@
           <t>SRC</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -1528,6 +2318,11 @@
           <t>S 600F SX</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -1535,6 +2330,11 @@
           <t>SAFE KIT CDR/868</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -1542,6 +2342,11 @@
           <t>S 600F DX</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -1549,6 +2354,11 @@
           <t>NOIRE 2</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -1556,6 +2366,11 @@
           <t>RMS 435/2</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -1563,6 +2378,11 @@
           <t>TAG SX</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -1570,6 +2390,11 @@
           <t>COM 215 50</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -1577,6 +2402,11 @@
           <t>TAG DX</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -1584,6 +2414,11 @@
           <t>BLADE 3</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -1591,6 +2426,11 @@
           <t>RQM 504/BD2</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -1598,6 +2438,11 @@
           <t>BLADE 3/24</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -1605,6 +2450,11 @@
           <t>BLADE 5</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -1612,6 +2462,11 @@
           <t>RQM 508/BD2</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -1619,6 +2474,11 @@
           <t>BL TOW 24</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -1626,6 +2486,11 @@
           <t>BLADE 5/24</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -1633,6 +2498,11 @@
           <t>EDGE 230/R4</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -1640,6 +2510,11 @@
           <t>EL UMS1</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -1647,6 +2522,11 @@
           <t>EVO 1200</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -1654,6 +2534,11 @@
           <t>KIT ACE 601/24</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -1661,6 +2546,11 @@
           <t>KIT EVO 600/CRV4</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -1668,6 +2558,11 @@
           <t>LPX LAMP/WH</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -1675,6 +2570,11 @@
           <t>NC L16</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -1682,6 +2582,11 @@
           <t>NOIRE 4</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -1689,6 +2594,11 @@
           <t>RQM 449/2</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -1696,6 +2606,11 @@
           <t>SNAP 5/6</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -1703,6 +2618,11 @@
           <t>SNAPPER 4</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -1710,6 +2630,11 @@
           <t>SSB 504</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -1717,6 +2642,11 @@
           <t>SUN POWER</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -1724,6 +2654,11 @@
           <t>T 624</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -1731,6 +2666,11 @@
           <t>TXQ 449/2</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -1738,6 +2678,11 @@
           <t>ZEN GC/1</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -1745,6 +2690,11 @@
           <t>CH 161M24</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -1752,6 +2702,11 @@
           <t>CH 86 P</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -1759,6 +2714,11 @@
           <t>CRS6</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -1766,6 +2726,11 @@
           <t>KIT MULTI DRIVE PRO 1800</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -1773,6 +2738,11 @@
           <t>SOLO 2</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -1780,6 +2750,11 @@
           <t>STAR BOX OC/2</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -1787,6 +2762,11 @@
           <t>SWING 300/EDGE</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -1794,6 +2774,11 @@
           <t>C65 KIT</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -1801,6 +2786,11 @@
           <t>C65/H</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -1808,6 +2798,11 @@
           <t>KANO 2/F</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -1815,6 +2810,11 @@
           <t>KANO 21/75</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -1822,6 +2822,11 @@
           <t>COM 170</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -1829,6 +2834,11 @@
           <t>COM 213</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -1836,6 +2846,11 @@
           <t>COM 310 80</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -1843,6 +2858,11 @@
           <t>COM 4C M</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -1850,6 +2870,11 @@
           <t>SLX 624</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -1857,6 +2882,11 @@
           <t>INTPRG-WF</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -1864,6 +2894,11 @@
           <t>KIT EVO 600/449/CRV4</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -1871,6 +2906,11 @@
           <t>SSB 508</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -1878,6 +2918,11 @@
           <t>KIT EVO 600/504/CRV4</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -1885,6 +2930,11 @@
           <t>NC L20</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -1892,6 +2942,11 @@
           <t>CH 155M20</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -1899,6 +2954,11 @@
           <t>NC L25</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -1906,6 +2966,11 @@
           <t>FM 402</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -1913,6 +2978,11 @@
           <t>RQM 486/2</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -1920,6 +2990,11 @@
           <t>SME</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -1927,6 +3002,11 @@
           <t>CH 130M16</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -1934,6 +3014,11 @@
           <t>NC L30</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -1941,6 +3026,11 @@
           <t>SNAPPER 5</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -1948,6 +3038,11 @@
           <t>BSH 61 L16</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -1955,6 +3050,11 @@
           <t>BSH 61 L20</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -1962,6 +3062,11 @@
           <t>CH 130M20</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -1969,6 +3074,11 @@
           <t>BSH 61 L25</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -1976,6 +3086,11 @@
           <t>APRO</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -1983,6 +3098,11 @@
           <t>BL TOW 24/VEZ</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -1990,6 +3110,11 @@
           <t>CC242EXTOPCB</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -1997,6 +3122,11 @@
           <t>EL UFS1</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2004,6 +3134,11 @@
           <t>ELDOM 3/4/5</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2011,6 +3146,11 @@
           <t>EVO 2000</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2018,6 +3158,11 @@
           <t>FM 404</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2025,6 +3170,11 @@
           <t>K-ROCK2HL</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2032,6 +3182,11 @@
           <t>KIT EVO 800</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2039,6 +3194,11 @@
           <t>KIT TOW 24</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2046,6 +3206,11 @@
           <t>NOIRE OC2</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2053,6 +3218,11 @@
           <t>RQM 504/2</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2060,6 +3230,11 @@
           <t>SLX 824</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2067,6 +3242,11 @@
           <t>SNAPPER 6</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2074,6 +3254,11 @@
           <t>TXQ 449/4</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2081,6 +3266,11 @@
           <t>CH 140 M16</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2088,6 +3278,11 @@
           <t>CH 162 M20</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2095,6 +3290,11 @@
           <t>CH 87 P</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2102,6 +3302,11 @@
           <t>CRM12</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2109,6 +3314,11 @@
           <t>HANDY</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2116,6 +3326,11 @@
           <t>REMOOTIO 3.0</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2123,6 +3338,11 @@
           <t>SWING 400/EDGE</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2130,6 +3350,11 @@
           <t>C65/F5 KIT</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2137,6 +3362,11 @@
           <t>KANO 11/5</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2144,6 +3374,11 @@
           <t>COM 169</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2151,6 +3386,11 @@
           <t>COM 300V 80</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2158,6 +3398,11 @@
           <t>COM 347 M</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2165,6 +3410,11 @@
           <t>KIT EVO 800/449</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2172,6 +3422,11 @@
           <t>KIT EVO 800/504</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2179,6 +3434,11 @@
           <t>RQM 508/2</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2186,6 +3446,11 @@
           <t>CC242EFAMCB</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -2193,6 +3458,11 @@
           <t>CK 200</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -2200,6 +3470,11 @@
           <t>EL 420</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -2207,6 +3482,11 @@
           <t>ELDOM 6/7/8</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -2214,6 +3494,11 @@
           <t>KIT EVO 1200</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -2221,6 +3506,11 @@
           <t>KIT SL 524</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -2228,6 +3518,11 @@
           <t>NOIRE RB2</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -2235,6 +3530,11 @@
           <t>SLX 1524</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -2242,6 +3542,11 @@
           <t>TXQ 486/2</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -2249,6 +3554,11 @@
           <t>CH 155M24</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -2256,6 +3566,11 @@
           <t>GSM MULTI ONE</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -2263,6 +3578,11 @@
           <t>SWING 600/EDGE</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -2270,6 +3590,11 @@
           <t>C65/8 KIT</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -2277,6 +3602,11 @@
           <t>KANO 11/5/F</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -2284,6 +3614,11 @@
           <t>COM 163 M18</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -2291,6 +3626,11 @@
           <t>COM 171</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -2298,6 +3638,11 @@
           <t>KIT EVO 1200/449</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -2305,6 +3650,11 @@
           <t>SWING 300/449</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -2312,6 +3662,11 @@
           <t>KIT RAP 4</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -2319,6 +3674,11 @@
           <t>KIT EVO 1200/504</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -2326,6 +3686,11 @@
           <t>SWING 400/449</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -2333,6 +3698,11 @@
           <t>SWING 600/449</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -2340,6 +3710,11 @@
           <t>SWING 300/504</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -2347,6 +3722,11 @@
           <t>MOLLIGHT 4X</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -2354,6 +3734,11 @@
           <t>SWING 400/504</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -2361,6 +3746,11 @@
           <t>SWING 600/504</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -2368,6 +3758,11 @@
           <t>SWING 300/T600</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -2375,6 +3770,11 @@
           <t>SWING 400/T600</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -2382,6 +3782,11 @@
           <t>SWING 600/T600</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -2389,6 +3794,11 @@
           <t>EL 601</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -2396,6 +3806,11 @@
           <t>ELV</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -2403,6 +3818,11 @@
           <t>FM OC/2</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -2410,6 +3830,11 @@
           <t>KIT BL 3924</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -2417,6 +3842,11 @@
           <t>KIT SLX 824</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -2424,6 +3854,11 @@
           <t>KIT TAG</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -2431,6 +3866,11 @@
           <t>MORPH 433/RM</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -2438,6 +3878,11 @@
           <t>SLX 3024</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -2445,6 +3890,11 @@
           <t>SNR SNAP</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -2452,6 +3902,11 @@
           <t>TXQ 486/4</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -2459,6 +3914,11 @@
           <t>GSM MULTI ONE KIT</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -2466,6 +3926,11 @@
           <t>C65/F8 KIT</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -2473,6 +3938,11 @@
           <t>KANO 6</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -2480,6 +3950,11 @@
           <t>COM 120 M18</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -2487,6 +3962,11 @@
           <t>COM 168</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -2494,6 +3974,11 @@
           <t>COM 300V 100</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -2501,6 +3986,11 @@
           <t>COM 315 100</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -2508,6 +3998,11 @@
           <t>COM 347 G</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -2515,6 +4010,11 @@
           <t>KIT SNAP 3</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -2522,6 +4022,11 @@
           <t>DOM 3 AS</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -2529,6 +4034,11 @@
           <t>GSM EASY</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -2536,6 +4046,11 @@
           <t>DOM 3</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -2543,6 +4058,11 @@
           <t>RPQ 449ITO</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -2550,6 +4070,11 @@
           <t>DRACO</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -2557,6 +4082,11 @@
           <t>FM 400 RB2</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -2564,6 +4094,11 @@
           <t>KEY CARD</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -2571,6 +4106,11 @@
           <t>KIT SLX 1524</t>
         </is>
       </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -2578,6 +4118,11 @@
           <t>POS 110</t>
         </is>
       </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -2585,6 +4130,11 @@
           <t>RPQ 504ITO</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -2592,6 +4142,11 @@
           <t>TXQ 504/2</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -2599,6 +4154,11 @@
           <t>CH 200</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -2606,6 +4166,11 @@
           <t>CH 325-60</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -2613,6 +4178,11 @@
           <t>RELÉ 2 OC/2</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -2620,6 +4190,11 @@
           <t>C65/H KIT</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -2627,6 +4202,11 @@
           <t>KANO 22/48</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -2634,6 +4214,11 @@
           <t>KANO 6/F</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -2641,6 +4226,11 @@
           <t>COM 86 P</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -2648,6 +4238,11 @@
           <t>KIT SNAP 4</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -2655,6 +4250,11 @@
           <t>FM 400 R4</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -2662,6 +4262,11 @@
           <t>RPQ 508ITO</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -2669,6 +4274,11 @@
           <t>BLEGOS</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -2676,6 +4286,11 @@
           <t>CARD</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -2683,6 +4298,11 @@
           <t>DOM 4</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -2690,6 +4310,11 @@
           <t>DRACO 2</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -2697,6 +4322,11 @@
           <t>FIX RAP4</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -2704,6 +4334,11 @@
           <t>KIT SLX 3024</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -2711,6 +4346,11 @@
           <t>RCQ 449ND</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -2718,6 +4358,11 @@
           <t>TXQ 504/4</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -2725,6 +4370,11 @@
           <t>CH 325-80</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -2732,6 +4382,11 @@
           <t>CH 325-Y60</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -2739,6 +4394,11 @@
           <t>GSM PRO CON CLOUD</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -2746,6 +4406,11 @@
           <t>C65/H/F5 KIT</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -2753,6 +4418,11 @@
           <t>KANO 11/8</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -2760,6 +4430,11 @@
           <t>KANO 22/60</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -2767,6 +4442,11 @@
           <t>COM 94 S</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -2774,6 +4454,11 @@
           <t>KIT SNAP 5</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -2781,6 +4466,11 @@
           <t>RCQ 504ND1</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -2788,6 +4478,11 @@
           <t>BLESOL</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -2795,6 +4490,11 @@
           <t>DOM 5</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -2802,6 +4502,11 @@
           <t>FIX SNAP</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -2809,6 +4514,11 @@
           <t>RCQ 508ND1</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -2816,6 +4526,11 @@
           <t>SEL 50</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -2823,6 +4538,11 @@
           <t>TXQ 504/8</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -2830,6 +4550,11 @@
           <t>C65/H/8 KIT</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -2837,6 +4562,11 @@
           <t>KANO 11/8/F</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -2844,6 +4574,11 @@
           <t>KANO 22/65</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -2851,6 +4586,11 @@
           <t>COM 327 80</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -2858,6 +4598,11 @@
           <t>KIT SNAP 6</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -2865,6 +4610,11 @@
           <t>ANT 433</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -2872,6 +4622,11 @@
           <t>ANS 400</t>
         </is>
       </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -2879,6 +4634,11 @@
           <t>BASEDOM 3/4/5</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -2886,6 +4646,11 @@
           <t>DKS TPT</t>
         </is>
       </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -2893,6 +4658,11 @@
           <t>DOM 6</t>
         </is>
       </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -2900,6 +4670,11 @@
           <t>RCQ 433//WF</t>
         </is>
       </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -2907,6 +4682,11 @@
           <t>SEL 120</t>
         </is>
       </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -2914,6 +4694,11 @@
           <t>TXQ 504 BD2</t>
         </is>
       </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -2921,6 +4706,11 @@
           <t>CH 202</t>
         </is>
       </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -2928,6 +4718,11 @@
           <t>C65/H/F8 KIT</t>
         </is>
       </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -2935,6 +4730,11 @@
           <t>KANO 22/75</t>
         </is>
       </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -2942,6 +4742,11 @@
           <t>KANO 75/5</t>
         </is>
       </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -2949,6 +4754,11 @@
           <t>KIT ELDOM 3</t>
         </is>
       </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -2956,6 +4766,11 @@
           <t>BASEDOM 6/7/8</t>
         </is>
       </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -2963,6 +4778,11 @@
           <t>KIT BLADE EASY</t>
         </is>
       </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -2970,6 +4790,11 @@
           <t>KIT BLADE</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -2977,6 +4802,11 @@
           <t>KIT BLADE/24</t>
         </is>
       </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -2984,6 +4814,11 @@
           <t>DKS DUAL</t>
         </is>
       </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -2991,6 +4826,11 @@
           <t>DOM 7</t>
         </is>
       </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -2998,6 +4838,11 @@
           <t>KIT BLEGOS</t>
         </is>
       </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -3005,6 +4850,11 @@
           <t>LED SNAPPER 3</t>
         </is>
       </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -3012,6 +4862,11 @@
           <t>SEL 120/D</t>
         </is>
       </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -3019,6 +4874,11 @@
           <t>TXQ 504 BD4</t>
         </is>
       </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -3026,6 +4886,11 @@
           <t>CH 332-80</t>
         </is>
       </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -3033,6 +4898,11 @@
           <t>C75 KIT</t>
         </is>
       </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -3040,6 +4910,11 @@
           <t>KANO 75/5/F</t>
         </is>
       </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -3047,6 +4922,11 @@
           <t>COM 155 M24</t>
         </is>
       </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -3054,6 +4934,11 @@
           <t>COM 325V 80</t>
         </is>
       </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -3061,6 +4946,11 @@
           <t>KIT ELDOM 4</t>
         </is>
       </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -3068,6 +4958,11 @@
           <t>DKS DUALT</t>
         </is>
       </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -3075,6 +4970,11 @@
           <t>DOM 8</t>
         </is>
       </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -3082,6 +4982,11 @@
           <t>LED SNAPPER 4</t>
         </is>
       </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -3089,6 +4994,11 @@
           <t>TXQ 508/2</t>
         </is>
       </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -3096,6 +5006,11 @@
           <t>CH 332-Y80</t>
         </is>
       </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -3103,6 +5018,11 @@
           <t>C75/F5 KIT</t>
         </is>
       </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -3110,6 +5030,11 @@
           <t>KANO 75/8</t>
         </is>
       </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -3117,6 +5042,11 @@
           <t>COM 332 80</t>
         </is>
       </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -3124,6 +5054,11 @@
           <t>KIT ELDOM 5</t>
         </is>
       </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -3131,6 +5066,11 @@
           <t>LED SNAPPER 5</t>
         </is>
       </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -3138,6 +5078,11 @@
           <t>LED SNAPPER 6</t>
         </is>
       </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -3145,6 +5090,11 @@
           <t>PROXI</t>
         </is>
       </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -3152,6 +5102,11 @@
           <t>TXQ 508/4</t>
         </is>
       </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -3159,6 +5114,11 @@
           <t>CH 332-Y100</t>
         </is>
       </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -3166,6 +5126,11 @@
           <t>C75/8 KIT</t>
         </is>
       </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -3173,6 +5138,11 @@
           <t>KANO 75/8/F</t>
         </is>
       </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -3180,6 +5150,11 @@
           <t>COM 346 G</t>
         </is>
       </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -3187,6 +5162,11 @@
           <t>KIT ELDOM 6</t>
         </is>
       </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -3194,6 +5174,11 @@
           <t>LED DOM 3</t>
         </is>
       </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -3201,6 +5186,11 @@
           <t>TXQ 508/8</t>
         </is>
       </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -3208,6 +5198,11 @@
           <t>C75/F8 KIT</t>
         </is>
       </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -3215,6 +5210,11 @@
           <t>KANO 23/40</t>
         </is>
       </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -3222,6 +5222,11 @@
           <t>CA 9999/M</t>
         </is>
       </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -3229,6 +5234,11 @@
           <t>KIT ELDOM 7</t>
         </is>
       </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -3236,6 +5246,11 @@
           <t>LED DOM 4</t>
         </is>
       </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -3243,6 +5258,11 @@
           <t>TXQ 508 BD2</t>
         </is>
       </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -3250,6 +5270,11 @@
           <t>C75/H KIT</t>
         </is>
       </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -3257,6 +5282,11 @@
           <t>KANO 23/60</t>
         </is>
       </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -3264,6 +5294,11 @@
           <t>COM 332 120</t>
         </is>
       </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -3271,6 +5306,11 @@
           <t>KIT ELDOM 8</t>
         </is>
       </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -3278,6 +5318,11 @@
           <t>LED DOM 5</t>
         </is>
       </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -3285,6 +5330,11 @@
           <t>TXQ 508 BD4</t>
         </is>
       </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -3292,6 +5342,11 @@
           <t>C75/H/F5 KIT</t>
         </is>
       </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -3299,6 +5354,11 @@
           <t>COM 334 100</t>
         </is>
       </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -3306,6 +5366,11 @@
           <t>LED DOM 6</t>
         </is>
       </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -3313,6 +5378,11 @@
           <t>MORPH 433/T2</t>
         </is>
       </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -3320,6 +5390,11 @@
           <t>C75/H/8 KIT</t>
         </is>
       </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -3327,6 +5402,11 @@
           <t>COM 333V 100</t>
         </is>
       </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -3334,6 +5414,11 @@
           <t>LED DOM 7</t>
         </is>
       </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -3341,6 +5426,11 @@
           <t>MORPH 433/T4</t>
         </is>
       </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -3348,6 +5438,11 @@
           <t>CH 337-Y80</t>
         </is>
       </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -3355,6 +5450,11 @@
           <t>C75/H/F8 KIT</t>
         </is>
       </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -3362,6 +5462,11 @@
           <t>COM 184 M18</t>
         </is>
       </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -3369,6 +5474,11 @@
           <t>LED DOM 8</t>
         </is>
       </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -3376,6 +5486,11 @@
           <t>MORPH 433T4/A</t>
         </is>
       </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -3383,6 +5498,11 @@
           <t>CH 337-Y90</t>
         </is>
       </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -3390,6 +5510,11 @@
           <t>COM 90 B</t>
         </is>
       </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -3397,6 +5522,11 @@
           <t>DOM SP-YE</t>
         </is>
       </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -3404,6 +5534,11 @@
           <t>TXQ PRO 449/4</t>
         </is>
       </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -3411,6 +5546,11 @@
           <t>CH 337-Y100</t>
         </is>
       </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -3418,6 +5558,11 @@
           <t>DOM SP-GR</t>
         </is>
       </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -3425,6 +5570,11 @@
           <t>TXQ PRO 449/4A</t>
         </is>
       </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -3432,6 +5582,11 @@
           <t>COM 337 100</t>
         </is>
       </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -3439,6 +5594,11 @@
           <t>DOM SP-RE</t>
         </is>
       </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -3446,6 +5606,11 @@
           <t>DOM SP-WH</t>
         </is>
       </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -3453,6 +5618,11 @@
           <t>DOM SP-BR</t>
         </is>
       </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -3460,6 +5630,11 @@
           <t>DOM SP-BL</t>
         </is>
       </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -3467,6 +5642,11 @@
           <t>CH 190</t>
         </is>
       </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -3474,6 +5654,11 @@
           <t>COM 190 30</t>
         </is>
       </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -3481,6 +5666,11 @@
           <t>DOM SP-2OR</t>
         </is>
       </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -3488,6 +5678,11 @@
           <t>COM 338 100</t>
         </is>
       </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -3495,6 +5690,11 @@
           <t>COM 336V 100</t>
         </is>
       </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -3502,6 +5702,11 @@
           <t>CH 230/25</t>
         </is>
       </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -3509,6 +5714,11 @@
           <t>CH 230/31</t>
         </is>
       </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -3516,6 +5726,11 @@
           <t>CH 230/40</t>
         </is>
       </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -3523,6 +5738,11 @@
           <t>COM 245 35</t>
         </is>
       </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -3530,6 +5750,11 @@
           <t>CH 240</t>
         </is>
       </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -3537,6 +5762,11 @@
           <t>CH 247</t>
         </is>
       </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -3544,6 +5774,11 @@
           <t>COM 247</t>
         </is>
       </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -3551,6 +5786,11 @@
           <t>COM 255-350</t>
         </is>
       </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -3558,6 +5798,11 @@
           <t>ACC HL 360</t>
         </is>
       </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -3565,6 +5810,11 @@
           <t>ACC HLXCORE 360</t>
         </is>
       </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -3572,6 +5822,11 @@
           <t>ACE 601 VEZ</t>
         </is>
       </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -3579,6 +5834,11 @@
           <t>ANQ 800</t>
         </is>
       </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -3586,6 +5846,11 @@
           <t>BL 3924</t>
         </is>
       </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -3593,6 +5858,11 @@
           <t>BL 3924 ARM</t>
         </is>
       </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -3600,6 +5870,11 @@
           <t>BL 3924 DRM</t>
         </is>
       </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -3607,6 +5882,11 @@
           <t>BL 3924/VEZ</t>
         </is>
       </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -3614,6 +5894,11 @@
           <t>BLTS24DRM</t>
         </is>
       </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -3621,6 +5906,11 @@
           <t>CARDIN CARD</t>
         </is>
       </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -3628,6 +5918,11 @@
           <t>CDR RED</t>
         </is>
       </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -3635,6 +5930,11 @@
           <t>COVERMIX 200</t>
         </is>
       </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -3642,6 +5942,11 @@
           <t>COVERMIX 400</t>
         </is>
       </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -3649,6 +5954,11 @@
           <t>COVERMIX 5002</t>
         </is>
       </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -3656,6 +5966,11 @@
           <t>COVERMIX 5004</t>
         </is>
       </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -3663,6 +5978,11 @@
           <t>CRL 170E</t>
         </is>
       </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -3670,6 +5990,11 @@
           <t>CRL 360 DE</t>
         </is>
       </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -3677,6 +6002,11 @@
           <t>DKS 1000</t>
         </is>
       </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -3684,6 +6014,11 @@
           <t>DKS 1000T</t>
         </is>
       </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -3691,6 +6026,11 @@
           <t>DKS TPM</t>
         </is>
       </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -3698,6 +6038,11 @@
           <t>DKSTPMT</t>
         </is>
       </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -3705,6 +6050,11 @@
           <t>EDGE 2 ELŐLAP</t>
         </is>
       </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -3712,6 +6062,11 @@
           <t>EDGE 2 TOK</t>
         </is>
       </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -3719,6 +6074,11 @@
           <t>EDGE 4 ELŐLAP</t>
         </is>
       </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -3726,6 +6086,11 @@
           <t>EDGE 4 TOK</t>
         </is>
       </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -3733,6 +6098,11 @@
           <t>EDGE GUMIFÜL</t>
         </is>
       </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -3740,6 +6110,11 @@
           <t>EDGE HÁTLAP</t>
         </is>
       </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -3747,6 +6122,11 @@
           <t>EL SRA</t>
         </is>
       </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -3754,6 +6134,11 @@
           <t>EL SRS</t>
         </is>
       </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -3761,6 +6146,11 @@
           <t>HL BOX/C</t>
         </is>
       </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -3768,6 +6158,11 @@
           <t>HL BOX/I</t>
         </is>
       </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -3775,6 +6170,11 @@
           <t>HLXCORE 230</t>
         </is>
       </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -3782,6 +6182,11 @@
           <t>HOT</t>
         </is>
       </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -3789,6 +6194,11 @@
           <t>INTPRG-4G10</t>
         </is>
       </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -3796,6 +6206,11 @@
           <t>KABEL</t>
         </is>
       </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -3803,6 +6218,11 @@
           <t>KBNIMH 1</t>
         </is>
       </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -3810,6 +6230,11 @@
           <t>KBNIMH D</t>
         </is>
       </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -3817,6 +6242,11 @@
           <t>KIT BLESTEVO</t>
         </is>
       </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -3824,6 +6254,11 @@
           <t>KIT HL XCORE 230</t>
         </is>
       </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -3831,6 +6266,11 @@
           <t>KIT HL XCORE 24</t>
         </is>
       </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -3838,6 +6278,11 @@
           <t>KIT S504</t>
         </is>
       </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -3845,6 +6290,11 @@
           <t>KIT S504BD</t>
         </is>
       </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -3852,6 +6302,11 @@
           <t>KIT SLX 624</t>
         </is>
       </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -3859,6 +6314,11 @@
           <t>KULCS BLADE</t>
         </is>
       </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -3866,6 +6326,11 @@
           <t>KULCS TELCOMA</t>
         </is>
       </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -3873,6 +6338,11 @@
           <t>MCC 449 R1</t>
         </is>
       </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -3880,6 +6350,11 @@
           <t>MCC MORPH HM1</t>
         </is>
       </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -3887,6 +6362,11 @@
           <t>MEM 16</t>
         </is>
       </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -3894,6 +6374,11 @@
           <t>METALDEC 230</t>
         </is>
       </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -3901,6 +6386,11 @@
           <t>MOD BT</t>
         </is>
       </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -3908,6 +6398,11 @@
           <t>MOD BT TELCOMA</t>
         </is>
       </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -3915,6 +6410,11 @@
           <t>MOD CA</t>
         </is>
       </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -3922,6 +6422,11 @@
           <t>MOLLIGHT 4</t>
         </is>
       </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -3929,6 +6434,11 @@
           <t>MORPH KEY/CB</t>
         </is>
       </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -3936,6 +6446,11 @@
           <t>PAF</t>
         </is>
       </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -3943,6 +6458,11 @@
           <t>PASSO TS</t>
         </is>
       </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -3950,6 +6470,11 @@
           <t>PG BASE/500</t>
         </is>
       </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -3957,6 +6482,11 @@
           <t>POS 110/D</t>
         </is>
       </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -3964,6 +6494,11 @@
           <t>POS 50</t>
         </is>
       </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -3971,6 +6506,11 @@
           <t>PTE</t>
         </is>
       </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -3978,6 +6518,11 @@
           <t>RCQ 433/4G</t>
         </is>
       </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -3985,6 +6530,11 @@
           <t>RCQ 868/4G</t>
         </is>
       </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -3992,6 +6542,11 @@
           <t>RPQ 504/T10</t>
         </is>
       </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -3999,6 +6554,11 @@
           <t>RPQ 508/T10</t>
         </is>
       </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -4006,6 +6566,11 @@
           <t>RVS</t>
         </is>
       </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -4013,6 +6578,11 @@
           <t>SAFE CDR8</t>
         </is>
       </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -4020,6 +6590,11 @@
           <t>SBL HL</t>
         </is>
       </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -4027,6 +6602,11 @@
           <t>SEL FIX</t>
         </is>
       </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -4034,6 +6614,11 @@
           <t>SELINT BT8</t>
         </is>
       </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -4041,6 +6626,11 @@
           <t>SL524VEZ.999471</t>
         </is>
       </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -4048,6 +6638,11 @@
           <t>SLX 1524-3024 VEZ</t>
         </is>
       </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -4055,6 +6650,11 @@
           <t>SLX 824 VEZ</t>
         </is>
       </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -4062,6 +6662,11 @@
           <t>SNAP4 RSN24</t>
         </is>
       </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -4069,6 +6674,11 @@
           <t>SRA</t>
         </is>
       </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -4076,6 +6686,11 @@
           <t>SRC RX</t>
         </is>
       </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -4083,6 +6698,11 @@
           <t>SRC TX</t>
         </is>
       </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -4090,6 +6710,11 @@
           <t>STRIP LED 5</t>
         </is>
       </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -4097,6 +6722,11 @@
           <t>SUN POWER PLUS</t>
         </is>
       </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -4104,6 +6734,11 @@
           <t>TRQ 738/2</t>
         </is>
       </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -4111,6 +6746,11 @@
           <t>TS 20</t>
         </is>
       </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -4118,6 +6758,11 @@
           <t>TS 30</t>
         </is>
       </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -4125,6 +6770,11 @@
           <t>TS 40</t>
         </is>
       </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -4132,6 +6782,11 @@
           <t>TS 60</t>
         </is>
       </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -4139,6 +6794,11 @@
           <t>TX WALL 500 MFB</t>
         </is>
       </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -4146,6 +6806,11 @@
           <t>TX WALL 500 MFL</t>
         </is>
       </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -4153,6 +6818,11 @@
           <t>TXEDGE 2 TOK</t>
         </is>
       </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -4160,6 +6830,11 @@
           <t>TXEDGE 4 TOK</t>
         </is>
       </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -4167,6 +6842,11 @@
           <t>TXQ 449/2 TOK</t>
         </is>
       </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -4174,6 +6854,11 @@
           <t>TXQ 449/4 TOK</t>
         </is>
       </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -4181,6 +6866,11 @@
           <t>TXQ PRO 508/4</t>
         </is>
       </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -4188,6 +6878,11 @@
           <t>UNICO500MF</t>
         </is>
       </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -4195,6 +6890,11 @@
           <t>YPR124SCL00</t>
         </is>
       </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -4202,6 +6902,11 @@
           <t>Z124</t>
         </is>
       </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -4209,6 +6914,11 @@
           <t>ZRA 3</t>
         </is>
       </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -4216,6 +6926,11 @@
           <t>ZRL 7</t>
         </is>
       </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -4223,6 +6938,11 @@
           <t>CH 230/35</t>
         </is>
       </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -4230,6 +6950,11 @@
           <t>CH 255</t>
         </is>
       </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -4237,6 +6962,11 @@
           <t>CH 337-100 D20</t>
         </is>
       </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -4244,6 +6974,11 @@
           <t>CR2016</t>
         </is>
       </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -4251,6 +6986,11 @@
           <t>CR2032</t>
         </is>
       </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -4258,6 +6998,11 @@
           <t>CR2430</t>
         </is>
       </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -4265,6 +7010,11 @@
           <t>GP23AE</t>
         </is>
       </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -4272,6 +7022,11 @@
           <t>GP27A</t>
         </is>
       </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -4279,6 +7034,11 @@
           <t>GSM AC/DC ADAPT</t>
         </is>
       </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -4286,6 +7046,11 @@
           <t>GSM AC/DC PANEL</t>
         </is>
       </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -4293,6 +7058,11 @@
           <t>GSM AKKU</t>
         </is>
       </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -4300,6 +7070,11 @@
           <t>GSM PRO BOX</t>
         </is>
       </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -4307,6 +7082,11 @@
           <t>GSM PS230</t>
         </is>
       </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -4314,6 +7094,11 @@
           <t>GSM USB KIT</t>
         </is>
       </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -4321,6 +7106,11 @@
           <t>GW 44207</t>
         </is>
       </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -4328,6 +7118,11 @@
           <t>KIT FS 1500</t>
         </is>
       </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -4335,6 +7130,11 @@
           <t>KONDI 10UF</t>
         </is>
       </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -4342,6 +7142,11 @@
           <t>KONDI 12UF</t>
         </is>
       </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -4349,6 +7154,11 @@
           <t>KONDI 14UF</t>
         </is>
       </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -4356,6 +7166,11 @@
           <t>KONDI 16UF</t>
         </is>
       </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -4363,6 +7178,11 @@
           <t>KONDI 20UF</t>
         </is>
       </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -4370,6 +7190,11 @@
           <t>KONDI 8UF</t>
         </is>
       </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -4377,6 +7202,11 @@
           <t>PADAVAN</t>
         </is>
       </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -4384,6 +7214,11 @@
           <t>RC 2 WIFI</t>
         </is>
       </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -4391,6 +7226,11 @@
           <t>REMOOTIO CM</t>
         </is>
       </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -4398,6 +7238,11 @@
           <t>REMOOTIO CM 2.0</t>
         </is>
       </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -4405,6 +7250,11 @@
           <t>REMOOTIO DB</t>
         </is>
       </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -4412,6 +7262,11 @@
           <t>REMOOTIO INSIDE</t>
         </is>
       </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -4419,6 +7274,11 @@
           <t>SOM AUT 400/30</t>
         </is>
       </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -4426,6 +7286,11 @@
           <t>SOM AUT 400/40</t>
         </is>
       </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -4433,6 +7298,11 @@
           <t>SOM OPTO</t>
         </is>
       </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -4440,6 +7310,11 @@
           <t>TECHNOLOGATE SW KIT</t>
         </is>
       </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -4447,6 +7322,11 @@
           <t>TX WIFI</t>
         </is>
       </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -4454,6 +7334,11 @@
           <t>C48 6M</t>
         </is>
       </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -4461,6 +7346,11 @@
           <t>C75</t>
         </is>
       </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -4468,6 +7358,11 @@
           <t>C75 1M</t>
         </is>
       </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -4475,6 +7370,11 @@
           <t>C75/H</t>
         </is>
       </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -4482,6 +7382,11 @@
           <t>KANO 11/6</t>
         </is>
       </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -4489,6 +7394,11 @@
           <t>KANO 11/6/F</t>
         </is>
       </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -4496,6 +7406,11 @@
           <t>KANO A/TALP</t>
         </is>
       </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -4503,6 +7418,11 @@
           <t>KANO A/TALP/75</t>
         </is>
       </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -4510,6 +7430,11 @@
           <t>KANO B/TALP</t>
         </is>
       </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -4517,6 +7442,11 @@
           <t>KANO B/TALP/75</t>
         </is>
       </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -4524,6 +7454,11 @@
           <t>KANO F/TALP</t>
         </is>
       </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -4531,6 +7466,11 @@
           <t>KANO F/TALP/75</t>
         </is>
       </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -4538,6 +7478,11 @@
           <t>KANO H/TALP</t>
         </is>
       </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -4545,6 +7490,11 @@
           <t>KANO H/TALP/75</t>
         </is>
       </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -4552,6 +7502,11 @@
           <t>CA 100/100</t>
         </is>
       </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -4559,6 +7514,11 @@
           <t>CA 100/120</t>
         </is>
       </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -4566,6 +7526,11 @@
           <t>CA 100/140</t>
         </is>
       </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -4573,6 +7538,11 @@
           <t>CA 100/80</t>
         </is>
       </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -4580,6 +7550,11 @@
           <t>CA 262/100</t>
         </is>
       </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -4587,6 +7562,11 @@
           <t>CA 262/150</t>
         </is>
       </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -4594,6 +7574,11 @@
           <t>CA 340/100</t>
         </is>
       </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -4601,6 +7586,11 @@
           <t>CA 340/40</t>
         </is>
       </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -4608,6 +7598,11 @@
           <t>CA 340/60</t>
         </is>
       </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -4615,6 +7610,11 @@
           <t>CA 340/80</t>
         </is>
       </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -4622,6 +7622,11 @@
           <t>CA 345/P</t>
         </is>
       </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -4629,6 +7634,11 @@
           <t>CA 346/P</t>
         </is>
       </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -4636,6 +7646,11 @@
           <t>CA 370 Z/P</t>
         </is>
       </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -4643,6 +7658,11 @@
           <t>CA 375/16</t>
         </is>
       </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -4650,6 +7670,11 @@
           <t>CA 375/18</t>
         </is>
       </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -4657,6 +7682,11 @@
           <t>CA 375/20</t>
         </is>
       </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -4664,6 +7694,11 @@
           <t>CA 376/16</t>
         </is>
       </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -4671,6 +7706,11 @@
           <t>CA 376/18</t>
         </is>
       </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -4678,6 +7718,11 @@
           <t>CA 376/20</t>
         </is>
       </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -4685,6 +7730,11 @@
           <t>CA 377/16</t>
         </is>
       </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -4692,6 +7742,11 @@
           <t>CA 380 F/G</t>
         </is>
       </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -4699,6 +7754,11 @@
           <t>CA 396/G</t>
         </is>
       </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -4706,6 +7766,11 @@
           <t>CA 396/M</t>
         </is>
       </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -4713,6 +7778,11 @@
           <t>CA 397/G</t>
         </is>
       </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -4720,6 +7790,11 @@
           <t>CA 397/M</t>
         </is>
       </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -4727,6 +7802,11 @@
           <t>CA 399/M6</t>
         </is>
       </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -4734,6 +7814,11 @@
           <t>CA 399Z/G6</t>
         </is>
       </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -4741,6 +7826,11 @@
           <t>CA 399Z/M6</t>
         </is>
       </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -4748,6 +7838,11 @@
           <t>CA 400/100</t>
         </is>
       </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -4755,6 +7850,11 @@
           <t>CA 400/60</t>
         </is>
       </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -4762,6 +7862,11 @@
           <t>CA 400/80</t>
         </is>
       </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -4769,6 +7874,11 @@
           <t>CA 400/80/20</t>
         </is>
       </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -4776,6 +7886,11 @@
           <t>CA 401/100</t>
         </is>
       </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -4783,6 +7898,11 @@
           <t>CA 401/120</t>
         </is>
       </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -4790,6 +7910,11 @@
           <t>CA 401/60</t>
         </is>
       </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -4797,6 +7922,11 @@
           <t>CA 401/80</t>
         </is>
       </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -4804,6 +7934,11 @@
           <t>CA 410/100</t>
         </is>
       </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -4811,6 +7946,11 @@
           <t>CA 410/60</t>
         </is>
       </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -4818,6 +7958,11 @@
           <t>CA 410/80</t>
         </is>
       </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -4825,6 +7970,11 @@
           <t>CA 410/80/20</t>
         </is>
       </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -4832,6 +7982,11 @@
           <t>CA 411/100</t>
         </is>
       </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -4839,6 +7994,11 @@
           <t>CA 411/60</t>
         </is>
       </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -4846,6 +8006,11 @@
           <t>CA 411/80</t>
         </is>
       </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -4853,6 +8018,11 @@
           <t>CA 415/100</t>
         </is>
       </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -4860,6 +8030,11 @@
           <t>CA 415/60</t>
         </is>
       </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -4867,6 +8042,11 @@
           <t>CA 415/80</t>
         </is>
       </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -4874,6 +8054,11 @@
           <t>CA 416/100</t>
         </is>
       </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -4881,6 +8066,11 @@
           <t>CA 416/60</t>
         </is>
       </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -4888,6 +8078,11 @@
           <t>CA 416/80</t>
         </is>
       </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -4895,6 +8090,11 @@
           <t>CA 425/100</t>
         </is>
       </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -4902,6 +8102,11 @@
           <t>CA 425/100/20</t>
         </is>
       </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -4909,6 +8114,11 @@
           <t>CA 425/60</t>
         </is>
       </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -4916,6 +8126,11 @@
           <t>CA 425/80</t>
         </is>
       </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -4923,6 +8138,11 @@
           <t>CA 425/80/20</t>
         </is>
       </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -4930,6 +8150,11 @@
           <t>CA 426/100</t>
         </is>
       </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -4937,6 +8162,11 @@
           <t>CA 426/60</t>
         </is>
       </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -4944,6 +8174,11 @@
           <t>CA 426/80</t>
         </is>
       </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -4951,6 +8186,11 @@
           <t>CA 448/35X30</t>
         </is>
       </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -4958,6 +8198,11 @@
           <t>CA 461</t>
         </is>
       </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -4965,6 +8210,11 @@
           <t>CA 462/G</t>
         </is>
       </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -4972,6 +8222,11 @@
           <t>CA 471.G</t>
         </is>
       </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -4979,6 +8234,11 @@
           <t>CA 472/60</t>
         </is>
       </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -4986,6 +8246,11 @@
           <t>CA 752/M</t>
         </is>
       </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -4993,6 +8258,11 @@
           <t>CA 754/M</t>
         </is>
       </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -5000,6 +8270,11 @@
           <t>CA 813</t>
         </is>
       </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -5007,6 +8282,11 @@
           <t>CA 850/18</t>
         </is>
       </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -5014,6 +8294,11 @@
           <t>CA 902/16X3</t>
         </is>
       </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -5021,6 +8306,11 @@
           <t>CA 902/20X3</t>
         </is>
       </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -5028,6 +8318,11 @@
           <t>CA 904/16X3</t>
         </is>
       </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -5035,6 +8330,11 @@
           <t>CA 906/3</t>
         </is>
       </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -5042,6 +8342,11 @@
           <t>CA 920/M</t>
         </is>
       </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -5049,6 +8354,11 @@
           <t>CA 9999/G</t>
         </is>
       </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -5056,6 +8366,11 @@
           <t>ALBATROS-100-G</t>
         </is>
       </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -5063,6 +8378,11 @@
           <t>ALBATROS-100-P</t>
         </is>
       </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -5070,6 +8390,11 @@
           <t>COM 290</t>
         </is>
       </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -5077,6 +8402,11 @@
           <t>COM 291</t>
         </is>
       </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -5084,6 +8414,11 @@
           <t>COM 295</t>
         </is>
       </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -5091,6 +8426,11 @@
           <t>COM 297</t>
         </is>
       </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -5098,6 +8438,11 @@
           <t>COM 2C M</t>
         </is>
       </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -5105,6 +8450,11 @@
           <t>COM 32-34</t>
         </is>
       </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -5112,6 +8462,11 @@
           <t>COM 345 P/A</t>
         </is>
       </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -5119,6 +8474,11 @@
           <t>COM 35G</t>
         </is>
       </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -5126,6 +8486,11 @@
           <t>COM CG-40</t>
         </is>
       </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -5133,6 +8498,11 @@
           <t>COM CGA 347P</t>
         </is>
       </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -5140,6 +8510,11 @@
           <t>COM RS-100F</t>
         </is>
       </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -5147,6 +8522,11 @@
           <t>RANGER2-100-50</t>
         </is>
       </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -5154,6 +8534,11 @@
           <t>RANGER3-120-50</t>
         </is>
       </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -5161,6 +8546,11 @@
           <t>KULCS GR</t>
         </is>
       </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -5168,6 +8558,11 @@
           <t>COM 338 200</t>
         </is>
       </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -5175,6 +8570,11 @@
           <t>BL GRIFFE</t>
         </is>
       </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -5182,6 +8582,11 @@
           <t>BL GRIFFE VEZ</t>
         </is>
       </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -5189,6 +8594,11 @@
           <t>HLXCORE 24</t>
         </is>
       </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -5196,6 +8606,11 @@
           <t>KBNIMH-T1</t>
         </is>
       </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -5203,6 +8618,11 @@
           <t>KIT BL GRIFFE</t>
         </is>
       </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -5210,6 +8630,11 @@
           <t>KULCS 1401</t>
         </is>
       </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -5217,6 +8642,11 @@
           <t>KULCS BLUES</t>
         </is>
       </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -5224,6 +8654,11 @@
           <t>CA 752/P</t>
         </is>
       </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -5231,6 +8666,11 @@
           <t>FORCE 3300 SÍN</t>
         </is>
       </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -5238,6 +8678,11 @@
           <t>FORCE 3800 SÍN</t>
         </is>
       </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -5245,6 +8690,11 @@
           <t>FORCE 4F</t>
         </is>
       </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -5252,6 +8702,11 @@
           <t>FORCE 500 AC</t>
         </is>
       </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -5259,6 +8714,11 @@
           <t>FORCE 800 AC</t>
         </is>
       </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -5266,6 +8726,11 @@
           <t>FORCE BASE 70</t>
         </is>
       </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -5273,6 +8738,11 @@
           <t>FORCE BATTERY BB1</t>
         </is>
       </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -5280,6 +8750,11 @@
           <t>FORCE CABLE 8M</t>
         </is>
       </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -5287,6 +8762,11 @@
           <t>FORCE F-RV</t>
         </is>
       </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -5294,6 +8774,11 @@
           <t>FORCE FC 120</t>
         </is>
       </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -5301,6 +8786,11 @@
           <t>FORCE FS SÍN</t>
         </is>
       </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -5308,6 +8798,11 @@
           <t>FORCE KÖZÉPSŐ ADAPTER</t>
         </is>
       </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -5315,6 +8810,11 @@
           <t>FORCE PC</t>
         </is>
       </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -5322,6 +8822,11 @@
           <t>FORCE PC REFLEX</t>
         </is>
       </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -5329,6 +8834,11 @@
           <t>FORCE RB4 WP</t>
         </is>
       </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -5336,6 +8846,11 @@
           <t>FORCE RC</t>
         </is>
       </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -5343,6 +8858,11 @@
           <t>FORCE SD PROTECTION</t>
         </is>
       </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -5350,6 +8870,11 @@
           <t>FORCE SÍN ADAPTER</t>
         </is>
       </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -5357,6 +8882,11 @@
           <t>FOTO TER</t>
         </is>
       </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -5364,6 +8894,11 @@
           <t>KIT ULTIMATE 600/SP PRO</t>
         </is>
       </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -5371,6 +8906,11 @@
           <t>MULTI DRIVE PRO 1000N</t>
         </is>
       </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -5378,6 +8918,11 @@
           <t>MULTI DRIVE PRO 1800N</t>
         </is>
       </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -5385,6 +8930,11 @@
           <t>PC 190U</t>
         </is>
       </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -5392,6 +8942,11 @@
           <t>TERRIER DX</t>
         </is>
       </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -5399,6 +8954,11 @@
           <t>TERRIER SX</t>
         </is>
       </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -5406,6 +8966,11 @@
           <t>FORCE F-BOX</t>
         </is>
       </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -5413,6 +8978,11 @@
           <t>FORCE F-CAM</t>
         </is>
       </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -5420,6 +8990,11 @@
           <t>FORCE SE-TX</t>
         </is>
       </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -5427,6 +9002,11 @@
           <t>FORCE STOP BUTTON</t>
         </is>
       </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -5434,6 +9014,11 @@
           <t>FORCE W E-LOCK</t>
         </is>
       </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -5441,6 +9026,11 @@
           <t>FORCE W-OSE</t>
         </is>
       </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -5448,6 +9038,11 @@
           <t>FORCE W-OSE KIT</t>
         </is>
       </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -5455,6 +9050,11 @@
           <t>FORCE W-PC</t>
         </is>
       </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -5462,11 +9062,21 @@
           <t>FORCE W-TS</t>
         </is>
       </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
           <t>FORCE W-TX</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/safehome_data.xlsx
+++ b/safehome_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:C722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +478,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +495,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +512,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +529,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +546,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +563,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +580,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +597,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +614,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +631,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +648,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +665,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +682,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +699,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +716,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,6 +733,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -655,6 +750,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -667,6 +767,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -679,6 +784,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -691,6 +801,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -703,6 +818,11 @@
           <t>551</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -715,6 +835,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -727,6 +852,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -739,6 +869,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -751,6 +886,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -763,6 +903,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -775,6 +920,11 @@
           <t>121</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -787,6 +937,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -799,6 +954,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -811,6 +971,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -823,6 +988,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -835,6 +1005,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -847,6 +1022,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -859,6 +1039,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -871,6 +1056,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -883,6 +1073,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -895,6 +1090,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -907,6 +1107,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -919,6 +1124,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -931,6 +1141,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -943,6 +1158,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,6 +1175,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -967,6 +1192,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -979,6 +1209,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -991,6 +1226,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1003,6 +1243,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1015,6 +1260,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1027,6 +1277,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1039,6 +1294,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1051,6 +1311,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1063,6 +1328,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1075,6 +1345,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1087,6 +1362,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1099,6 +1379,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1111,6 +1396,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1123,6 +1413,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1135,6 +1430,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1147,6 +1447,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1159,6 +1464,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1171,6 +1481,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1183,6 +1498,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1195,6 +1515,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1207,6 +1532,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1219,6 +1549,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1231,6 +1566,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1243,6 +1583,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1255,6 +1600,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1267,6 +1617,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1279,6 +1634,11 @@
           <t>1007</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1291,6 +1651,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1303,6 +1668,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1315,6 +1685,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1327,6 +1702,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1339,6 +1719,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1351,6 +1736,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1363,6 +1753,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1375,6 +1770,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1387,6 +1787,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1399,6 +1804,11 @@
           <t>484</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1411,6 +1821,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1423,6 +1838,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1435,6 +1855,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1447,6 +1872,11 @@
           <t>732</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1459,6 +1889,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1471,6 +1906,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1483,6 +1923,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1495,6 +1940,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1507,6 +1957,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1519,6 +1974,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1531,6 +1991,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1543,6 +2008,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1555,6 +2025,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1567,6 +2042,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1579,6 +2059,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1591,6 +2076,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1603,6 +2093,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1615,6 +2110,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1627,6 +2127,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1639,6 +2144,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1651,6 +2161,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1663,6 +2178,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1675,6 +2195,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1687,6 +2212,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1699,6 +2229,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1711,6 +2246,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1723,6 +2263,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1735,6 +2280,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1747,6 +2297,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1759,6 +2314,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1771,6 +2331,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1783,6 +2348,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1795,6 +2365,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1807,6 +2382,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1819,6 +2399,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1831,6 +2416,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1843,6 +2433,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1855,6 +2450,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1867,6 +2467,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1879,6 +2484,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1891,6 +2501,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1903,6 +2518,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1915,6 +2535,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1927,6 +2552,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1939,6 +2569,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1951,6 +2586,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1963,6 +2603,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1975,6 +2620,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1987,6 +2637,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1999,6 +2654,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2011,6 +2671,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2023,6 +2688,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2035,6 +2705,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2047,6 +2722,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2059,6 +2739,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2071,6 +2756,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2083,6 +2773,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2095,6 +2790,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2107,6 +2807,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2119,6 +2824,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2131,6 +2841,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2143,6 +2858,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2155,6 +2875,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2167,6 +2892,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2179,6 +2909,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2191,6 +2926,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2203,6 +2943,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2215,6 +2960,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2227,6 +2977,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2239,6 +2994,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2251,6 +3011,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2263,6 +3028,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2275,6 +3045,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2287,6 +3062,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2299,6 +3079,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2311,6 +3096,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2323,6 +3113,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2335,6 +3130,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2347,6 +3147,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2359,6 +3164,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2371,6 +3181,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2383,6 +3198,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2395,6 +3215,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2407,6 +3232,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2419,6 +3249,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2431,6 +3266,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2443,6 +3283,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2455,6 +3300,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2467,6 +3317,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2479,6 +3334,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2491,6 +3351,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2503,6 +3368,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2515,6 +3385,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2527,6 +3402,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2539,6 +3419,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2551,6 +3436,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2563,6 +3453,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2575,6 +3470,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2587,6 +3487,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2599,6 +3504,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2611,6 +3521,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2623,6 +3538,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2635,6 +3555,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2647,6 +3572,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2659,6 +3589,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2671,6 +3606,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2683,6 +3623,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2695,6 +3640,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2707,6 +3657,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2719,6 +3674,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2731,6 +3691,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2743,6 +3708,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2755,6 +3725,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2767,6 +3742,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2779,6 +3759,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2791,6 +3776,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2803,6 +3793,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2815,6 +3810,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2827,6 +3827,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2839,6 +3844,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2851,6 +3861,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2863,6 +3878,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2875,6 +3895,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2887,6 +3912,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2899,6 +3929,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2911,6 +3946,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2923,6 +3963,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2935,6 +3980,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2947,6 +3997,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2959,6 +4014,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2971,6 +4031,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2983,6 +4048,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2995,6 +4065,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3007,6 +4082,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3019,6 +4099,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3031,6 +4116,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3043,6 +4133,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3055,6 +4150,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3067,6 +4167,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3079,6 +4184,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3091,6 +4201,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3103,6 +4218,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3115,6 +4235,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3127,6 +4252,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3139,6 +4269,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3151,6 +4286,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3163,6 +4303,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3175,6 +4320,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3187,6 +4337,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3199,6 +4354,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3211,6 +4371,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3223,6 +4388,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3235,6 +4405,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3247,6 +4422,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3259,6 +4439,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3271,6 +4456,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3283,6 +4473,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3295,6 +4490,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3307,6 +4507,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3319,6 +4524,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3331,6 +4541,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3343,6 +4558,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3355,6 +4575,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3367,6 +4592,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3379,6 +4609,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3391,6 +4626,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3403,6 +4643,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3415,6 +4660,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3427,6 +4677,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3439,6 +4694,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3451,6 +4711,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3463,6 +4728,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3475,6 +4745,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3487,6 +4762,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3499,6 +4779,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3511,6 +4796,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3523,6 +4813,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3535,6 +4830,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3547,6 +4847,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3559,6 +4864,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3571,6 +4881,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3583,6 +4898,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3595,6 +4915,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3607,6 +4932,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3619,6 +4949,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3631,6 +4966,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3643,6 +4983,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3655,6 +5000,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3667,6 +5017,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3679,6 +5034,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3691,6 +5051,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3703,6 +5068,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3715,6 +5085,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3727,6 +5102,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3739,6 +5119,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3751,6 +5136,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3763,6 +5153,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3775,6 +5170,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3787,6 +5187,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3799,6 +5204,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3811,6 +5221,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3823,6 +5238,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3835,6 +5255,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3847,6 +5272,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3859,6 +5289,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3871,6 +5306,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3883,6 +5323,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3895,6 +5340,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3907,6 +5357,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3919,6 +5374,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3931,6 +5391,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3943,6 +5408,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3955,6 +5425,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3967,6 +5442,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3979,6 +5459,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3991,6 +5476,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -4003,6 +5493,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -4015,6 +5510,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -4027,6 +5527,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -4039,6 +5544,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -4051,6 +5561,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -4063,6 +5578,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -4075,6 +5595,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -4087,6 +5612,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -4099,6 +5629,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -4111,6 +5646,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -4123,6 +5663,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -4135,6 +5680,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -4147,6 +5697,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4159,6 +5714,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4171,6 +5731,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4183,6 +5748,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4195,6 +5765,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4207,6 +5782,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4219,6 +5799,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4231,6 +5816,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4243,6 +5833,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4255,6 +5850,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4267,6 +5867,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4279,6 +5884,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4291,6 +5901,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4303,6 +5918,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4315,6 +5935,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4327,6 +5952,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4339,6 +5969,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4351,6 +5986,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4363,6 +6003,11 @@
           <t>481</t>
         </is>
       </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4375,6 +6020,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4387,6 +6037,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4399,6 +6054,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4411,6 +6071,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4423,6 +6088,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4435,6 +6105,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4447,6 +6122,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4459,6 +6139,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4471,6 +6156,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4483,6 +6173,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4495,6 +6190,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4507,6 +6207,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4519,6 +6224,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4531,6 +6241,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4543,6 +6258,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4555,6 +6275,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4567,6 +6292,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4579,6 +6309,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4591,6 +6326,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -4603,6 +6343,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4615,6 +6360,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4627,6 +6377,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4639,6 +6394,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4651,6 +6411,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4663,6 +6428,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4675,6 +6445,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -4687,6 +6462,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4699,6 +6479,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4711,6 +6496,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4723,6 +6513,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4735,6 +6530,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4747,6 +6547,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4759,6 +6564,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4771,6 +6581,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4783,6 +6598,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4795,6 +6615,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -4807,6 +6632,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -4819,6 +6649,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -4831,6 +6666,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -4843,6 +6683,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -4855,6 +6700,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -4867,6 +6717,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -4879,6 +6734,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -4891,6 +6751,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -4903,6 +6768,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -4915,6 +6785,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -4927,6 +6802,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -4939,6 +6819,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -4951,6 +6836,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -4963,6 +6853,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -4975,6 +6870,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -4987,6 +6887,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -4999,6 +6904,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -5011,6 +6921,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -5023,6 +6938,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -5035,6 +6955,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -5047,6 +6972,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -5059,6 +6989,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -5071,6 +7006,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -5083,6 +7023,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -5095,6 +7040,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -5107,6 +7057,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -5119,6 +7074,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -5131,6 +7091,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -5143,6 +7108,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -5155,6 +7125,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -5167,6 +7142,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -5179,6 +7159,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -5191,6 +7176,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -5203,6 +7193,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -5215,6 +7210,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -5227,6 +7227,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -5239,6 +7244,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -5251,6 +7261,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -5263,6 +7278,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -5275,6 +7295,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -5287,6 +7312,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -5299,6 +7329,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -5311,6 +7346,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -5323,6 +7363,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -5335,6 +7380,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -5347,6 +7397,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -5359,6 +7414,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -5371,6 +7431,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -5383,6 +7448,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -5395,6 +7465,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -5407,6 +7482,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -5419,6 +7499,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -5431,6 +7516,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -5443,6 +7533,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -5455,6 +7550,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -5467,6 +7567,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -5479,6 +7584,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -5491,6 +7601,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -5503,6 +7618,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -5515,6 +7635,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -5527,6 +7652,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -5539,6 +7669,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -5551,6 +7686,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -5563,6 +7703,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -5575,6 +7720,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -5587,6 +7737,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -5599,6 +7754,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -5611,6 +7771,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -5623,6 +7788,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -5635,6 +7805,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -5647,6 +7822,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -5659,6 +7839,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -5671,6 +7856,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -5683,6 +7873,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -5695,6 +7890,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -5707,6 +7907,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -5719,6 +7924,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -5731,6 +7941,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -5743,6 +7958,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -5755,6 +7975,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -5767,6 +7992,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -5779,6 +8009,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -5791,6 +8026,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -5803,6 +8043,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -5815,6 +8060,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -5827,6 +8077,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -5839,6 +8094,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -5851,6 +8111,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -5863,6 +8128,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -5875,6 +8145,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -5887,6 +8162,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -5899,6 +8179,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -5911,6 +8196,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -5923,6 +8213,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -5935,6 +8230,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -5947,6 +8247,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -5959,6 +8264,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -5971,6 +8281,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -5983,6 +8298,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -5995,6 +8315,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -6007,6 +8332,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -6019,6 +8349,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -6031,6 +8366,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -6043,6 +8383,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -6055,6 +8400,11 @@
           <t>548</t>
         </is>
       </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -6067,6 +8417,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -6079,6 +8434,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -6091,6 +8451,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -6103,6 +8468,11 @@
           <t>366</t>
         </is>
       </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -6115,6 +8485,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -6127,6 +8502,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -6139,6 +8519,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -6151,6 +8536,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -6163,6 +8553,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -6175,6 +8570,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -6187,6 +8587,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -6199,6 +8604,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -6211,6 +8621,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -6223,6 +8638,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -6235,6 +8655,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -6247,6 +8672,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -6259,6 +8689,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -6271,6 +8706,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -6283,6 +8723,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -6295,6 +8740,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -6307,6 +8757,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -6319,6 +8774,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -6331,6 +8791,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -6343,6 +8808,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -6355,6 +8825,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -6367,6 +8842,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -6379,6 +8859,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -6391,6 +8876,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -6403,6 +8893,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -6415,6 +8910,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -6427,6 +8927,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -6439,6 +8944,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -6451,6 +8961,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -6463,6 +8978,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -6475,6 +8995,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -6487,6 +9012,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -6499,6 +9029,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -6511,6 +9046,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -6523,6 +9063,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -6535,6 +9080,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -6547,6 +9097,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -6559,6 +9114,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -6571,6 +9131,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -6583,6 +9148,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -6595,6 +9165,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -6607,6 +9182,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -6619,6 +9199,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -6631,6 +9216,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -6643,6 +9233,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -6655,6 +9250,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -6667,6 +9267,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -6679,6 +9284,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -6691,6 +9301,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -6703,6 +9318,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -6715,6 +9335,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -6727,6 +9352,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -6739,6 +9369,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -6751,6 +9386,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -6763,6 +9403,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -6775,6 +9420,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -6787,6 +9437,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -6799,6 +9454,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -6811,6 +9471,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -6823,6 +9488,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -6835,6 +9505,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -6847,6 +9522,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -6859,6 +9539,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -6871,6 +9556,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -6883,6 +9573,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -6895,6 +9590,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -6907,6 +9607,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -6919,6 +9624,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -6931,6 +9641,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -6943,6 +9658,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -6955,6 +9675,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -6967,6 +9692,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -6979,6 +9709,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -6991,6 +9726,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -7003,6 +9743,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -7015,6 +9760,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -7027,6 +9777,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -7039,6 +9794,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -7051,6 +9811,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -7063,6 +9828,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -7075,6 +9845,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -7087,6 +9862,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -7099,6 +9879,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -7111,6 +9896,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -7123,6 +9913,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -7135,6 +9930,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -7147,6 +9947,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -7159,6 +9964,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -7171,6 +9981,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -7183,6 +9998,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -7195,6 +10015,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -7207,6 +10032,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -7219,6 +10049,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -7231,6 +10066,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -7243,6 +10083,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -7255,6 +10100,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -7267,6 +10117,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -7279,6 +10134,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -7291,6 +10151,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -7303,6 +10168,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -7315,6 +10185,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -7327,6 +10202,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -7339,6 +10219,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -7351,6 +10236,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -7363,6 +10253,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -7375,6 +10270,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -7387,6 +10287,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -7399,6 +10304,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -7411,6 +10321,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -7423,6 +10338,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -7435,6 +10355,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -7447,6 +10372,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -7459,6 +10389,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -7471,6 +10406,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -7483,6 +10423,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -7495,6 +10440,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -7507,6 +10457,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -7519,6 +10474,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -7531,6 +10491,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -7543,6 +10508,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -7555,6 +10525,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -7567,6 +10542,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -7579,6 +10559,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -7591,6 +10576,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -7603,6 +10593,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -7615,6 +10610,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -7627,6 +10627,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -7639,6 +10644,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -7651,6 +10661,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -7663,6 +10678,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -7675,6 +10695,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -7687,6 +10712,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -7699,6 +10729,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -7711,6 +10746,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -7723,6 +10763,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -7735,6 +10780,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -7747,6 +10797,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -7759,6 +10814,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -7771,6 +10831,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -7783,6 +10848,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -7795,6 +10865,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -7807,6 +10882,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -7819,6 +10899,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -7831,6 +10916,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -7843,6 +10933,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -7855,6 +10950,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -7867,6 +10967,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -7879,6 +10984,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -7891,6 +11001,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -7903,6 +11018,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -7915,6 +11035,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -7927,6 +11052,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -7939,6 +11069,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -7951,6 +11086,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -7963,6 +11103,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -7975,6 +11120,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -7987,6 +11137,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -7999,6 +11154,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -8011,6 +11171,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -8023,6 +11188,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -8035,6 +11205,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -8047,6 +11222,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -8059,6 +11239,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -8071,6 +11256,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -8083,6 +11273,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -8095,6 +11290,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -8107,6 +11307,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -8119,6 +11324,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -8131,6 +11341,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -8143,6 +11358,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -8155,6 +11375,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -8167,6 +11392,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -8179,6 +11409,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -8191,6 +11426,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -8203,6 +11443,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -8215,6 +11460,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -8227,6 +11477,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -8239,6 +11494,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -8251,6 +11511,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -8263,6 +11528,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -8275,6 +11545,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -8287,6 +11562,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -8299,6 +11579,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -8311,6 +11596,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -8323,6 +11613,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -8335,6 +11630,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -8347,6 +11647,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -8359,6 +11664,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -8371,6 +11681,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -8383,6 +11698,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -8395,6 +11715,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -8407,6 +11732,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -8419,6 +11749,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -8431,6 +11766,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -8443,6 +11783,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -8455,6 +11800,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -8467,6 +11817,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -8479,6 +11834,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -8491,6 +11851,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -8503,6 +11868,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -8515,6 +11885,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -8527,6 +11902,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -8539,6 +11919,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -8551,6 +11936,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -8563,6 +11953,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -8575,6 +11970,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -8587,6 +11987,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -8599,6 +12004,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -8611,6 +12021,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -8623,6 +12038,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -8635,6 +12055,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -8647,6 +12072,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -8659,6 +12089,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -8671,6 +12106,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -8683,6 +12123,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -8695,6 +12140,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -8707,6 +12157,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -8719,6 +12174,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -8731,6 +12191,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -8743,6 +12208,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -8755,6 +12225,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -8767,6 +12242,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -8779,6 +12259,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -8791,6 +12276,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -8803,6 +12293,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -8815,6 +12310,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -8827,6 +12327,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -8839,6 +12344,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -8851,6 +12361,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -8863,6 +12378,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -8875,6 +12395,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -8887,6 +12412,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -8899,6 +12429,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -8911,6 +12446,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -8923,6 +12463,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -8935,6 +12480,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -8947,6 +12497,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -8959,6 +12514,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -8971,6 +12531,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -8983,6 +12548,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -8995,6 +12565,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -9007,6 +12582,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -9019,6 +12599,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -9031,6 +12616,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -9043,6 +12633,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -9055,6 +12650,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -9067,6 +12667,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -9075,6 +12680,11 @@
         </is>
       </c>
       <c r="B722" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
         <is>
           <t>6</t>
         </is>

--- a/safehome_data.xlsx
+++ b/safehome_data.xlsx
@@ -2269,7 +2269,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2465,3618 +2465,5066 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A722"/>
+  <dimension ref="A1:C723"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>50</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>51</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>55</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>61</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>63</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>67</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>78</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>79</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>83</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>85</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>86</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>90</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>92</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>93</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>96</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>97</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>102</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>106</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>113</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>123</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>132</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>134</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>135</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>136</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>137</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>139</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>141</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>142</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>144</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>145</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>146</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>148</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>150</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>152</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>154</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>155</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>156</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>157</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>159</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>160</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>161</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>163</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>165</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>166</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>171</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>172</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>173</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>174</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>175</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>176</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>177</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>178</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>180</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>181</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>182</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>183</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>184</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>187</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>188</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>189</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>190</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>192</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>193</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>194</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>195</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>196</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>197</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>198</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>199</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>200</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>201</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>204</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>205</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>206</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>207</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>209</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>211</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>212</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>213</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>214</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>216</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>219</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>220</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>221</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>222</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>227</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>228</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>229</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>230</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>231</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>232</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>233</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>234</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>235</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>236</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>238</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>239</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>240</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>241</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>242</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>243</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>244</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>245</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>246</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>247</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>248</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>249</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>251</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>252</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>253</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>254</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>255</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>256</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>257</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>258</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>259</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>260</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>262</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>263</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>264</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>265</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>266</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>267</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>268</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>270</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>272</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>273</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>275</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>276</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>277</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>278</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>279</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>280</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>281</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>283</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>284</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>285</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>286</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>287</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>288</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>289</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>290</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>291</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>292</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>293</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>294</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>295</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>296</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>297</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>298</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>299</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>300</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>301</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>302</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>303</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>304</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>305</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>306</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>307</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>308</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>309</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>310</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>311</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>312</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>314</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>315</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>316</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>317</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>318</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>319</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>320</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>321</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>322</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>323</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>324</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>325</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>326</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>327</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>328</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>329</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>331</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>333</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>334</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>335</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>336</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>337</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>338</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>339</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>340</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>341</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>342</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>343</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>344</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>345</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>346</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>347</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>349</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>350</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>351</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>352</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>353</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>354</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>355</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="B356" s="1"/>
+      <c r="C356" s="1"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>356</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="B357" s="1"/>
+      <c r="C357" s="1"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>357</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="B358" s="1"/>
+      <c r="C358" s="1"/>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>358</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="B359" s="1"/>
+      <c r="C359" s="1"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>359</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="B360" s="1"/>
+      <c r="C360" s="1"/>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>360</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="B361" s="1"/>
+      <c r="C361" s="1"/>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>361</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="B362" s="1"/>
+      <c r="C362" s="1"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>362</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="B363" s="1"/>
+      <c r="C363" s="1"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>363</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B364" s="1"/>
+      <c r="C364" s="1"/>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>364</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="B365" s="1"/>
+      <c r="C365" s="1"/>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>365</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B366" s="1"/>
+      <c r="C366" s="1"/>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>366</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="B367" s="1"/>
+      <c r="C367" s="1"/>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>367</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B368" s="1"/>
+      <c r="C368" s="1"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>368</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="B369" s="1"/>
+      <c r="C369" s="1"/>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>369</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="B370" s="1"/>
+      <c r="C370" s="1"/>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>370</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="B371" s="1"/>
+      <c r="C371" s="1"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>371</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="B372" s="1"/>
+      <c r="C372" s="1"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>372</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="B373" s="1"/>
+      <c r="C373" s="1"/>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>373</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="B374" s="1"/>
+      <c r="C374" s="1"/>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>374</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="B375" s="1"/>
+      <c r="C375" s="1"/>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>375</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="B376" s="1"/>
+      <c r="C376" s="1"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>376</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="B377" s="1"/>
+      <c r="C377" s="1"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>377</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="B378" s="1"/>
+      <c r="C378" s="1"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>378</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="B379" s="1"/>
+      <c r="C379" s="1"/>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>379</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="B380" s="1"/>
+      <c r="C380" s="1"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>380</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="B381" s="1"/>
+      <c r="C381" s="1"/>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>381</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="B382" s="1"/>
+      <c r="C382" s="1"/>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>382</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="B383" s="1"/>
+      <c r="C383" s="1"/>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>383</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="B384" s="1"/>
+      <c r="C384" s="1"/>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>384</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="B385" s="1"/>
+      <c r="C385" s="1"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>385</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="B386" s="1"/>
+      <c r="C386" s="1"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>386</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="B387" s="1"/>
+      <c r="C387" s="1"/>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>387</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="B388" s="1"/>
+      <c r="C388" s="1"/>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>388</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="B389" s="1"/>
+      <c r="C389" s="1"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>389</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="B390" s="1"/>
+      <c r="C390" s="1"/>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>390</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="B391" s="1"/>
+      <c r="C391" s="1"/>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>391</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="B392" s="1"/>
+      <c r="C392" s="1"/>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>392</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="B393" s="1"/>
+      <c r="C393" s="1"/>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>393</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="B394" s="1"/>
+      <c r="C394" s="1"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>394</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="B395" s="1"/>
+      <c r="C395" s="1"/>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>395</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="B396" s="1"/>
+      <c r="C396" s="1"/>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>396</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="B397" s="1"/>
+      <c r="C397" s="1"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>397</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="B398" s="1"/>
+      <c r="C398" s="1"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>398</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="B399" s="1"/>
+      <c r="C399" s="1"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>399</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="B400" s="1"/>
+      <c r="C400" s="1"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>400</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="B401" s="1"/>
+      <c r="C401" s="1"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>401</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="B402" s="1"/>
+      <c r="C402" s="1"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>402</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="B403" s="1"/>
+      <c r="C403" s="1"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>403</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="B404" s="1"/>
+      <c r="C404" s="1"/>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>404</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="B405" s="1"/>
+      <c r="C405" s="1"/>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>405</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="B406" s="1"/>
+      <c r="C406" s="1"/>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>406</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="B407" s="1"/>
+      <c r="C407" s="1"/>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>407</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="B408" s="1"/>
+      <c r="C408" s="1"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>408</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B409" s="1"/>
+      <c r="C409" s="1"/>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>409</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B410" s="1"/>
+      <c r="C410" s="1"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>410</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="B411" s="1"/>
+      <c r="C411" s="1"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>411</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B412" s="1"/>
+      <c r="C412" s="1"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>412</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="B413" s="1"/>
+      <c r="C413" s="1"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>413</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="B414" s="1"/>
+      <c r="C414" s="1"/>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>414</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="B415" s="1"/>
+      <c r="C415" s="1"/>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>415</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="B416" s="1"/>
+      <c r="C416" s="1"/>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>416</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="B417" s="1"/>
+      <c r="C417" s="1"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>417</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="B418" s="1"/>
+      <c r="C418" s="1"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>418</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="B419" s="1"/>
+      <c r="C419" s="1"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>419</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="B420" s="1"/>
+      <c r="C420" s="1"/>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>420</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="B421" s="1"/>
+      <c r="C421" s="1"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>421</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="B422" s="1"/>
+      <c r="C422" s="1"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>422</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="B423" s="1"/>
+      <c r="C423" s="1"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>423</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="B424" s="1"/>
+      <c r="C424" s="1"/>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>424</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="B425" s="1"/>
+      <c r="C425" s="1"/>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>425</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="B426" s="1"/>
+      <c r="C426" s="1"/>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>426</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="B427" s="1"/>
+      <c r="C427" s="1"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>427</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="B428" s="1"/>
+      <c r="C428" s="1"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>428</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="B429" s="1"/>
+      <c r="C429" s="1"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>429</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="B430" s="1"/>
+      <c r="C430" s="1"/>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>430</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="B431" s="1"/>
+      <c r="C431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>431</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="B432" s="1"/>
+      <c r="C432" s="1"/>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>432</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="B433" s="1"/>
+      <c r="C433" s="1"/>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>433</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="B434" s="1"/>
+      <c r="C434" s="1"/>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="B435" s="1"/>
+      <c r="C435" s="1"/>
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>435</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>436</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="B437" s="1"/>
+      <c r="C437" s="1"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>437</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>438</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>439</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>440</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>441</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B442" s="1"/>
+      <c r="C442" s="1"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>442</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="B443" s="1"/>
+      <c r="C443" s="1"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>443</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="B444" s="1"/>
+      <c r="C444" s="1"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>444</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="B445" s="1"/>
+      <c r="C445" s="1"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="B446" s="1"/>
+      <c r="C446" s="1"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>446</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="B447" s="1"/>
+      <c r="C447" s="1"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>447</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="B448" s="1"/>
+      <c r="C448" s="1"/>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>448</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="B449" s="1"/>
+      <c r="C449" s="1"/>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>449</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="B450" s="1"/>
+      <c r="C450" s="1"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>450</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="B451" s="1"/>
+      <c r="C451" s="1"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>451</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="B452" s="1"/>
+      <c r="C452" s="1"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>452</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="B453" s="1"/>
+      <c r="C453" s="1"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>453</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="B454" s="1"/>
+      <c r="C454" s="1"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>454</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="B455" s="1"/>
+      <c r="C455" s="1"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>455</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="B456" s="1"/>
+      <c r="C456" s="1"/>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>456</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="B457" s="1"/>
+      <c r="C457" s="1"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>457</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>458</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="B459" s="1"/>
+      <c r="C459" s="1"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>459</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="B460" s="1"/>
+      <c r="C460" s="1"/>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>460</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="B461" s="1"/>
+      <c r="C461" s="1"/>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>461</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="B462" s="1"/>
+      <c r="C462" s="1"/>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>462</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="B463" s="1"/>
+      <c r="C463" s="1"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>463</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="B464" s="1"/>
+      <c r="C464" s="1"/>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>464</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="B465" s="1"/>
+      <c r="C465" s="1"/>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>465</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="B466" s="1"/>
+      <c r="C466" s="1"/>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>466</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="B467" s="1"/>
+      <c r="C467" s="1"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>467</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="B468" s="1"/>
+      <c r="C468" s="1"/>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>468</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="B469" s="1"/>
+      <c r="C469" s="1"/>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>469</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="B470" s="1"/>
+      <c r="C470" s="1"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>470</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="B471" s="1"/>
+      <c r="C471" s="1"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>471</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B472" s="1"/>
+      <c r="C472" s="1"/>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>472</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="B473" s="1"/>
+      <c r="C473" s="1"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>473</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>474</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="B476" s="1"/>
+      <c r="C476" s="1"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>476</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="B477" s="1"/>
+      <c r="C477" s="1"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>477</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="B478" s="1"/>
+      <c r="C478" s="1"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>478</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="B479" s="1"/>
+      <c r="C479" s="1"/>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>479</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="B480" s="1"/>
+      <c r="C480" s="1"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>480</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="B481" s="1"/>
+      <c r="C481" s="1"/>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>481</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="B482" s="1"/>
+      <c r="C482" s="1"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>482</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="B483" s="1"/>
+      <c r="C483" s="1"/>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>483</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="B484" s="1"/>
+      <c r="C484" s="1"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>484</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="B485" s="1"/>
+      <c r="C485" s="1"/>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>485</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="B486" s="1"/>
+      <c r="C486" s="1"/>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>486</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="B487" s="1"/>
+      <c r="C487" s="1"/>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>487</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="B488" s="1"/>
+      <c r="C488" s="1"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>488</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="B489" s="1"/>
+      <c r="C489" s="1"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>489</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="B490" s="1"/>
+      <c r="C490" s="1"/>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>490</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="B491" s="1"/>
+      <c r="C491" s="1"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>491</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B492" s="1"/>
+      <c r="C492" s="1"/>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>492</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="B493" s="1"/>
+      <c r="C493" s="1"/>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>493</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="B494" s="1"/>
+      <c r="C494" s="1"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>494</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="B495" s="1"/>
+      <c r="C495" s="1"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>495</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="B496" s="1"/>
+      <c r="C496" s="1"/>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>496</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="B497" s="1"/>
+      <c r="C497" s="1"/>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>497</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="B498" s="1"/>
+      <c r="C498" s="1"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>498</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="B499" s="1"/>
+      <c r="C499" s="1"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>499</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="B500" s="1"/>
+      <c r="C500" s="1"/>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>500</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="B501" s="1"/>
+      <c r="C501" s="1"/>
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>501</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="B502" s="1"/>
+      <c r="C502" s="1"/>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>502</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="B503" s="1"/>
+      <c r="C503" s="1"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>503</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="B504" s="1"/>
+      <c r="C504" s="1"/>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>504</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="B505" s="1"/>
+      <c r="C505" s="1"/>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>505</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="B506" s="1"/>
+      <c r="C506" s="1"/>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="B507" s="1"/>
+      <c r="C507" s="1"/>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>507</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="B508" s="1"/>
+      <c r="C508" s="1"/>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>508</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="B509" s="1"/>
+      <c r="C509" s="1"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>509</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="B510" s="1"/>
+      <c r="C510" s="1"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>510</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="B511" s="1"/>
+      <c r="C511" s="1"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>511</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B512" s="1"/>
+      <c r="C512" s="1"/>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>512</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="B513" s="1"/>
+      <c r="C513" s="1"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>513</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="B514" s="1"/>
+      <c r="C514" s="1"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>514</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="B515" s="1"/>
+      <c r="C515" s="1"/>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>515</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="B516" s="1"/>
+      <c r="C516" s="1"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>516</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="B517" s="1"/>
+      <c r="C517" s="1"/>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>517</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="B518" s="1"/>
+      <c r="C518" s="1"/>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>518</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="B519" s="1"/>
+      <c r="C519" s="1"/>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>519</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="B520" s="1"/>
+      <c r="C520" s="1"/>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="B521" s="1"/>
+      <c r="C521" s="1"/>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>521</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="B522" s="1"/>
+      <c r="C522" s="1"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>522</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="B523" s="1"/>
+      <c r="C523" s="1"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>523</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="B524" s="1"/>
+      <c r="C524" s="1"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>524</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="B525" s="1"/>
+      <c r="C525" s="1"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>525</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="B526" s="1"/>
+      <c r="C526" s="1"/>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>526</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="B527" s="1"/>
+      <c r="C527" s="1"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>527</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="B528" s="1"/>
+      <c r="C528" s="1"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>528</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="B529" s="1"/>
+      <c r="C529" s="1"/>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>529</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="B530" s="1"/>
+      <c r="C530" s="1"/>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>530</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="B531" s="1"/>
+      <c r="C531" s="1"/>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>531</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="B532" s="1"/>
+      <c r="C532" s="1"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>532</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="B533" s="1"/>
+      <c r="C533" s="1"/>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>533</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="B534" s="1"/>
+      <c r="C534" s="1"/>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>534</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="B535" s="1"/>
+      <c r="C535" s="1"/>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>535</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="B536" s="1"/>
+      <c r="C536" s="1"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>536</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="B537" s="1"/>
+      <c r="C537" s="1"/>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>537</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="B538" s="1"/>
+      <c r="C538" s="1"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>538</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="B539" s="1"/>
+      <c r="C539" s="1"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>539</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="B540" s="1"/>
+      <c r="C540" s="1"/>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>540</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="B541" s="1"/>
+      <c r="C541" s="1"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>541</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="B542" s="1"/>
+      <c r="C542" s="1"/>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>542</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="B543" s="1"/>
+      <c r="C543" s="1"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>543</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="B544" s="1"/>
+      <c r="C544" s="1"/>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>544</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="B545" s="1"/>
+      <c r="C545" s="1"/>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>545</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="B546" s="1"/>
+      <c r="C546" s="1"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>546</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="B547" s="1"/>
+      <c r="C547" s="1"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>547</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="B548" s="1"/>
+      <c r="C548" s="1"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>548</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="B549" s="1"/>
+      <c r="C549" s="1"/>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>549</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="B550" s="1"/>
+      <c r="C550" s="1"/>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>550</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="B551" s="1"/>
+      <c r="C551" s="1"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>551</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="B552" s="1"/>
+      <c r="C552" s="1"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>552</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="B553" s="1"/>
+      <c r="C553" s="1"/>
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>553</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="B554" s="1"/>
+      <c r="C554" s="1"/>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>554</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="B555" s="1"/>
+      <c r="C555" s="1"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>555</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="B556" s="1"/>
+      <c r="C556" s="1"/>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>556</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="B557" s="1"/>
+      <c r="C557" s="1"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>557</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="B558" s="1"/>
+      <c r="C558" s="1"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>558</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="B559" s="1"/>
+      <c r="C559" s="1"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>559</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="B560" s="1"/>
+      <c r="C560" s="1"/>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>560</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="B561" s="1"/>
+      <c r="C561" s="1"/>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>561</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="B562" s="1"/>
+      <c r="C562" s="1"/>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>562</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="B563" s="1"/>
+      <c r="C563" s="1"/>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>563</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="B564" s="1"/>
+      <c r="C564" s="1"/>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>564</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="B565" s="1"/>
+      <c r="C565" s="1"/>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>565</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="B566" s="1"/>
+      <c r="C566" s="1"/>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>566</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="B567" s="1"/>
+      <c r="C567" s="1"/>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>567</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="B568" s="1"/>
+      <c r="C568" s="1"/>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>568</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="B569" s="1"/>
+      <c r="C569" s="1"/>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>569</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="B570" s="1"/>
+      <c r="C570" s="1"/>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>570</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="B571" s="1"/>
+      <c r="C571" s="1"/>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>571</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="B572" s="1"/>
+      <c r="C572" s="1"/>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>572</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="B573" s="1"/>
+      <c r="C573" s="1"/>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>573</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="B574" s="1"/>
+      <c r="C574" s="1"/>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>574</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="B575" s="1"/>
+      <c r="C575" s="1"/>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>575</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="B576" s="1"/>
+      <c r="C576" s="1"/>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>576</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="B577" s="1"/>
+      <c r="C577" s="1"/>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>577</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="B578" s="1"/>
+      <c r="C578" s="1"/>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>578</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="B579" s="1"/>
+      <c r="C579" s="1"/>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>579</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="B580" s="1"/>
+      <c r="C580" s="1"/>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>580</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="B581" s="1"/>
+      <c r="C581" s="1"/>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>581</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="B582" s="1"/>
+      <c r="C582" s="1"/>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>582</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="B583" s="1"/>
+      <c r="C583" s="1"/>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>583</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="B584" s="1"/>
+      <c r="C584" s="1"/>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>584</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="B585" s="1"/>
+      <c r="C585" s="1"/>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>585</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="B586" s="1"/>
+      <c r="C586" s="1"/>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>586</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="B587" s="1"/>
+      <c r="C587" s="1"/>
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>587</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="B588" s="1"/>
+      <c r="C588" s="1"/>
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>588</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="B589" s="1"/>
+      <c r="C589" s="1"/>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>589</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="B590" s="1"/>
+      <c r="C590" s="1"/>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>590</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="B591" s="1"/>
+      <c r="C591" s="1"/>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>591</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="B592" s="1"/>
+      <c r="C592" s="1"/>
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>592</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="B593" s="1"/>
+      <c r="C593" s="1"/>
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>593</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="B594" s="1"/>
+      <c r="C594" s="1"/>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>594</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="B595" s="1"/>
+      <c r="C595" s="1"/>
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>595</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="B596" s="1"/>
+      <c r="C596" s="1"/>
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>596</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="B597" s="1"/>
+      <c r="C597" s="1"/>
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>597</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="B598" s="1"/>
+      <c r="C598" s="1"/>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>598</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="B599" s="1"/>
+      <c r="C599" s="1"/>
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>599</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="B600" s="1"/>
+      <c r="C600" s="1"/>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>600</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="B601" s="1"/>
+      <c r="C601" s="1"/>
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>601</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="B602" s="1"/>
+      <c r="C602" s="1"/>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>602</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="B603" s="1"/>
+      <c r="C603" s="1"/>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>603</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="B604" s="1"/>
+      <c r="C604" s="1"/>
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>604</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="B605" s="1"/>
+      <c r="C605" s="1"/>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>605</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="B606" s="1"/>
+      <c r="C606" s="1"/>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>606</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="B607" s="1"/>
+      <c r="C607" s="1"/>
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>607</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="B608" s="1"/>
+      <c r="C608" s="1"/>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>608</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="B609" s="1"/>
+      <c r="C609" s="1"/>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>609</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="B610" s="1"/>
+      <c r="C610" s="1"/>
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>610</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="B611" s="1"/>
+      <c r="C611" s="1"/>
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>611</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="B612" s="1"/>
+      <c r="C612" s="1"/>
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>612</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="B613" s="1"/>
+      <c r="C613" s="1"/>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>613</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="B614" s="1"/>
+      <c r="C614" s="1"/>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>614</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="B615" s="1"/>
+      <c r="C615" s="1"/>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>615</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="B616" s="1"/>
+      <c r="C616" s="1"/>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>616</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="B617" s="1"/>
+      <c r="C617" s="1"/>
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>617</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="B618" s="1"/>
+      <c r="C618" s="1"/>
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>618</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="B619" s="1"/>
+      <c r="C619" s="1"/>
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>619</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="B620" s="1"/>
+      <c r="C620" s="1"/>
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>620</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="B621" s="1"/>
+      <c r="C621" s="1"/>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>621</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="B622" s="1"/>
+      <c r="C622" s="1"/>
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>622</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="B623" s="1"/>
+      <c r="C623" s="1"/>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>623</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="B624" s="1"/>
+      <c r="C624" s="1"/>
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>624</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="B625" s="1"/>
+      <c r="C625" s="1"/>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>625</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="B626" s="1"/>
+      <c r="C626" s="1"/>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>626</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="B627" s="1"/>
+      <c r="C627" s="1"/>
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>627</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="B628" s="1"/>
+      <c r="C628" s="1"/>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>628</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="B629" s="1"/>
+      <c r="C629" s="1"/>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>629</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="B630" s="1"/>
+      <c r="C630" s="1"/>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>630</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="B631" s="1"/>
+      <c r="C631" s="1"/>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>631</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="B632" s="1"/>
+      <c r="C632" s="1"/>
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>632</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="B633" s="1"/>
+      <c r="C633" s="1"/>
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>633</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="B634" s="1"/>
+      <c r="C634" s="1"/>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>634</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="B635" s="1"/>
+      <c r="C635" s="1"/>
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>635</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="B636" s="1"/>
+      <c r="C636" s="1"/>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>636</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="B637" s="1"/>
+      <c r="C637" s="1"/>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>637</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="B638" s="1"/>
+      <c r="C638" s="1"/>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>638</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="B639" s="1"/>
+      <c r="C639" s="1"/>
     </row>
     <row r="640" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>639</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="B640" s="1"/>
+      <c r="C640" s="1"/>
     </row>
     <row r="641" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>640</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="B641" s="1"/>
+      <c r="C641" s="1"/>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>641</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="B642" s="1"/>
+      <c r="C642" s="1"/>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>642</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="B643" s="1"/>
+      <c r="C643" s="1"/>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>643</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="B644" s="1"/>
+      <c r="C644" s="1"/>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>644</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="B645" s="1"/>
+      <c r="C645" s="1"/>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>645</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="B646" s="1"/>
+      <c r="C646" s="1"/>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>646</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="B647" s="1"/>
+      <c r="C647" s="1"/>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>647</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="B648" s="1"/>
+      <c r="C648" s="1"/>
     </row>
     <row r="649" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>648</v>
-      </c>
+        <v>647</v>
+      </c>
+      <c r="B649" s="1"/>
+      <c r="C649" s="1"/>
     </row>
     <row r="650" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>649</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="B650" s="1"/>
+      <c r="C650" s="1"/>
     </row>
     <row r="651" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>650</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="B651" s="1"/>
+      <c r="C651" s="1"/>
     </row>
     <row r="652" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>651</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="B652" s="1"/>
+      <c r="C652" s="1"/>
     </row>
     <row r="653" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>652</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="B653" s="1"/>
+      <c r="C653" s="1"/>
     </row>
     <row r="654" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>653</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="B654" s="1"/>
+      <c r="C654" s="1"/>
     </row>
     <row r="655" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>654</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="B655" s="1"/>
+      <c r="C655" s="1"/>
     </row>
     <row r="656" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>655</v>
-      </c>
+        <v>654</v>
+      </c>
+      <c r="B656" s="1"/>
+      <c r="C656" s="1"/>
     </row>
     <row r="657" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>656</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="B657" s="1"/>
+      <c r="C657" s="1"/>
     </row>
     <row r="658" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>657</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="B658" s="1"/>
+      <c r="C658" s="1"/>
     </row>
     <row r="659" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>658</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="B659" s="1"/>
+      <c r="C659" s="1"/>
     </row>
     <row r="660" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>659</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="B660" s="1"/>
+      <c r="C660" s="1"/>
     </row>
     <row r="661" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>660</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="B661" s="1"/>
+      <c r="C661" s="1"/>
     </row>
     <row r="662" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>661</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="B662" s="1"/>
+      <c r="C662" s="1"/>
     </row>
     <row r="663" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>662</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="B663" s="1"/>
+      <c r="C663" s="1"/>
     </row>
     <row r="664" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>663</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="B664" s="1"/>
+      <c r="C664" s="1"/>
     </row>
     <row r="665" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>664</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="B665" s="1"/>
+      <c r="C665" s="1"/>
     </row>
     <row r="666" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>665</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="B666" s="1"/>
+      <c r="C666" s="1"/>
     </row>
     <row r="667" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>666</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="B667" s="1"/>
+      <c r="C667" s="1"/>
     </row>
     <row r="668" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>667</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="B668" s="1"/>
+      <c r="C668" s="1"/>
     </row>
     <row r="669" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>668</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="B669" s="1"/>
+      <c r="C669" s="1"/>
     </row>
     <row r="670" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>669</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="B670" s="1"/>
+      <c r="C670" s="1"/>
     </row>
     <row r="671" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>670</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="B671" s="1"/>
+      <c r="C671" s="1"/>
     </row>
     <row r="672" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>671</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="B672" s="1"/>
+      <c r="C672" s="1"/>
     </row>
     <row r="673" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>672</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="B673" s="1"/>
+      <c r="C673" s="1"/>
     </row>
     <row r="674" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>673</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="B674" s="1"/>
+      <c r="C674" s="1"/>
     </row>
     <row r="675" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>674</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="B675" s="1"/>
+      <c r="C675" s="1"/>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>675</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="B676" s="1"/>
+      <c r="C676" s="1"/>
     </row>
     <row r="677" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>676</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="B677" s="1"/>
+      <c r="C677" s="1"/>
     </row>
     <row r="678" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>677</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="B678" s="1"/>
+      <c r="C678" s="1"/>
     </row>
     <row r="679" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>678</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="B679" s="1"/>
+      <c r="C679" s="1"/>
     </row>
     <row r="680" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>679</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="B680" s="1"/>
+      <c r="C680" s="1"/>
     </row>
     <row r="681" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>680</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="B681" s="1"/>
+      <c r="C681" s="1"/>
     </row>
     <row r="682" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>681</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="B682" s="1"/>
+      <c r="C682" s="1"/>
     </row>
     <row r="683" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>682</v>
-      </c>
+        <v>681</v>
+      </c>
+      <c r="B683" s="1"/>
+      <c r="C683" s="1"/>
     </row>
     <row r="684" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>683</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="B684" s="1"/>
+      <c r="C684" s="1"/>
     </row>
     <row r="685" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>684</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="B685" s="1"/>
+      <c r="C685" s="1"/>
     </row>
     <row r="686" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>685</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="B686" s="1"/>
+      <c r="C686" s="1"/>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>686</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="B687" s="1"/>
+      <c r="C687" s="1"/>
     </row>
     <row r="688" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>687</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="B688" s="1"/>
+      <c r="C688" s="1"/>
     </row>
     <row r="689" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>688</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="B689" s="1"/>
+      <c r="C689" s="1"/>
     </row>
     <row r="690" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>689</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="B690" s="1"/>
+      <c r="C690" s="1"/>
     </row>
     <row r="691" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>690</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="B691" s="1"/>
+      <c r="C691" s="1"/>
     </row>
     <row r="692" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>691</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="B692" s="1"/>
+      <c r="C692" s="1"/>
     </row>
     <row r="693" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>692</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="B693" s="1"/>
+      <c r="C693" s="1"/>
     </row>
     <row r="694" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>693</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="B694" s="1"/>
+      <c r="C694" s="1"/>
     </row>
     <row r="695" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>694</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="B695" s="1"/>
+      <c r="C695" s="1"/>
     </row>
     <row r="696" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>695</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="B696" s="1"/>
+      <c r="C696" s="1"/>
     </row>
     <row r="697" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>696</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="B697" s="1"/>
+      <c r="C697" s="1"/>
     </row>
     <row r="698" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>697</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="B698" s="1"/>
+      <c r="C698" s="1"/>
     </row>
     <row r="699" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>698</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="B699" s="1"/>
+      <c r="C699" s="1"/>
     </row>
     <row r="700" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>699</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="B700" s="1"/>
+      <c r="C700" s="1"/>
     </row>
     <row r="701" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>700</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="B701" s="1"/>
+      <c r="C701" s="1"/>
     </row>
     <row r="702" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>701</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="B702" s="1"/>
+      <c r="C702" s="1"/>
     </row>
     <row r="703" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>702</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="B703" s="1"/>
+      <c r="C703" s="1"/>
     </row>
     <row r="704" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>703</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="B704" s="1"/>
+      <c r="C704" s="1"/>
     </row>
     <row r="705" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>704</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="B705" s="1"/>
+      <c r="C705" s="1"/>
     </row>
     <row r="706" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>705</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="B706" s="1"/>
+      <c r="C706" s="1"/>
     </row>
     <row r="707" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>706</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="B707" s="1"/>
+      <c r="C707" s="1"/>
     </row>
     <row r="708" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>707</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="B708" s="1"/>
+      <c r="C708" s="1"/>
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>708</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="B709" s="1"/>
+      <c r="C709" s="1"/>
     </row>
     <row r="710" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>709</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="B710" s="1"/>
+      <c r="C710" s="1"/>
     </row>
     <row r="711" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>710</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="B711" s="1"/>
+      <c r="C711" s="1"/>
     </row>
     <row r="712" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>711</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="B712" s="1"/>
+      <c r="C712" s="1"/>
     </row>
     <row r="713" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>712</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="B713" s="1"/>
+      <c r="C713" s="1"/>
     </row>
     <row r="714" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>713</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="B714" s="1"/>
+      <c r="C714" s="1"/>
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>714</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="B715" s="1"/>
+      <c r="C715" s="1"/>
     </row>
     <row r="716" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>715</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="B716" s="1"/>
+      <c r="C716" s="1"/>
     </row>
     <row r="717" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>716</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="B717" s="1"/>
+      <c r="C717" s="1"/>
     </row>
     <row r="718" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>717</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="B718" s="1"/>
+      <c r="C718" s="1"/>
     </row>
     <row r="719" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>718</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="B719" s="1"/>
+      <c r="C719" s="1"/>
     </row>
     <row r="720" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>719</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="B720" s="1"/>
+      <c r="C720" s="1"/>
     </row>
     <row r="721" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>720</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="B721" s="1"/>
+      <c r="C721" s="1"/>
     </row>
     <row r="722" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B722" s="1"/>
+      <c r="C722" s="1"/>
+    </row>
+    <row r="723" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A723" s="1" t="s">
         <v>721</v>
       </c>
+      <c r="B723" s="1"/>
+      <c r="C723" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
